--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4898773.848326568</v>
+        <v>4936066.507998358</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7808335.093440536</v>
+        <v>7812364.083393907</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7808335.093440536</v>
+        <v>7812364.083393907</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3615241.141312588</v>
+        <v>3624506.764792538</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3615241.141312588</v>
+        <v>3624506.764792538</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41131713.27042431</v>
+        <v>41134251.0244188</v>
       </c>
     </row>
   </sheetData>
@@ -663,37 +663,37 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>403.6528496739509</v>
+        <v>3.652849673950868</v>
       </c>
       <c r="H2" t="n">
-        <v>406.9392164924722</v>
+        <v>40.431659417159</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>146.0515516424836</v>
       </c>
       <c r="J2" t="n">
         <v>390.8670435282804</v>
       </c>
       <c r="K2" t="n">
-        <v>732.0995645226478</v>
+        <v>781.7043316582914</v>
       </c>
       <c r="L2" t="n">
-        <v>45.93241495317329</v>
+        <v>728.9007806030273</v>
       </c>
       <c r="M2" t="n">
-        <v>795</v>
+        <v>260.6378258105779</v>
       </c>
       <c r="N2" t="n">
-        <v>795</v>
+        <v>156.9353044252684</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>439.8537369786343</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -702,28 +702,28 @@
         <v>340.6833447262534</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>244.3128802353297</v>
       </c>
       <c r="S2" t="n">
-        <v>116.323233559597</v>
+        <v>92.46635875709677</v>
       </c>
       <c r="T2" t="n">
         <v>186.2180339898704</v>
       </c>
       <c r="U2" t="n">
-        <v>249.2129347395654</v>
+        <v>649.2129347395654</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>143.8015708772849</v>
       </c>
       <c r="S3" t="n">
-        <v>221.6247713902901</v>
+        <v>65.52522637970566</v>
       </c>
       <c r="T3" t="n">
-        <v>5.132350123174206</v>
+        <v>405.1323501231742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2066805149037236</v>
+        <v>400.2066805149037</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>154.5581616145658</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -903,10 +903,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.652849673950868</v>
+        <v>37.1452925986377</v>
       </c>
       <c r="H5" t="n">
         <v>6.939216492472156</v>
@@ -915,13 +915,13 @@
         <v>146.0515516424836</v>
       </c>
       <c r="J5" t="n">
-        <v>779.1794999999998</v>
+        <v>390.8670435282804</v>
       </c>
       <c r="K5" t="n">
-        <v>15.22444699960824</v>
+        <v>15.22444699961384</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>778.5055477386934</v>
       </c>
       <c r="M5" t="n">
         <v>260.6378258105779</v>
@@ -930,37 +930,37 @@
         <v>156.9353044252684</v>
       </c>
       <c r="O5" t="n">
-        <v>766.6653681400852</v>
+        <v>795</v>
       </c>
       <c r="P5" t="n">
-        <v>780.2565776286211</v>
+        <v>361.7288545017321</v>
       </c>
       <c r="Q5" t="n">
         <v>340.6833447262534</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>244.3128802353297</v>
       </c>
       <c r="S5" t="n">
-        <v>92.46635875709677</v>
+        <v>492.4663587570968</v>
       </c>
       <c r="T5" t="n">
-        <v>586.2180339898704</v>
+        <v>186.2180339898704</v>
       </c>
       <c r="U5" t="n">
-        <v>527.0182578995818</v>
+        <v>249.2129347395654</v>
       </c>
       <c r="V5" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>165.9405481093475</v>
       </c>
       <c r="R6" t="n">
-        <v>143.8015708772849</v>
+        <v>185.4142736469535</v>
       </c>
       <c r="S6" t="n">
         <v>65.52522637970566</v>
@@ -1030,13 +1030,13 @@
         <v>0.2066805149037236</v>
       </c>
       <c r="V6" t="n">
-        <v>154.5581616145659</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1137,52 +1137,52 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
-        <v>184.4336232751825</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.6528496739509</v>
+        <v>3.652849673950868</v>
       </c>
       <c r="H8" t="n">
-        <v>406.9392164924722</v>
+        <v>6.939216492472156</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>146.0515516424836</v>
       </c>
       <c r="J8" t="n">
-        <v>779.1794999999998</v>
+        <v>390.8670435282804</v>
       </c>
       <c r="K8" t="n">
-        <v>64.82921413519205</v>
+        <v>781.7043316582914</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>795</v>
+        <v>260.6378258105779</v>
       </c>
       <c r="N8" t="n">
         <v>156.9353044252684</v>
       </c>
       <c r="O8" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>780.2565776286211</v>
       </c>
       <c r="Q8" t="n">
-        <v>508.6383491699233</v>
+        <v>729.1812846793111</v>
       </c>
       <c r="R8" t="n">
         <v>244.3128802353297</v>
       </c>
       <c r="S8" t="n">
-        <v>92.46635875709677</v>
+        <v>492.4663587570968</v>
       </c>
       <c r="T8" t="n">
-        <v>186.2180339898704</v>
+        <v>219.7104769145575</v>
       </c>
       <c r="U8" t="n">
         <v>249.2129347395654</v>
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1264,19 +1264,19 @@
         <v>5.132350123174206</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2066805149037236</v>
+        <v>400.2066805149037</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>229.7485401109616</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>178.9475819775265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1368,19 +1368,19 @@
         <v>260.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>228.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>189.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>183.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>183.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>15.73159601666973</v>
+        <v>182.6528496739509</v>
       </c>
       <c r="H11" t="n">
         <v>185.9392164924721</v>
@@ -1428,13 +1428,13 @@
         <v>408.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>417.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>371.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>290.3174326828064</v>
+        <v>220.0486372137682</v>
       </c>
     </row>
     <row r="12">
@@ -1562,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>318.4212312688555</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>238.9993129555745</v>
+        <v>237.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>206.4745782429939</v>
+        <v>205.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>167.3391557398498</v>
+        <v>166.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>161.3632896068686</v>
+        <v>160.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>153.2994076886985</v>
+        <v>160.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>159.6528496739509</v>
       </c>
       <c r="H14" t="n">
-        <v>163.9392164924721</v>
+        <v>162.9392164924721</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.312880235329658</v>
+        <v>0.3128802353296578</v>
       </c>
       <c r="S14" t="n">
-        <v>249.4663587570968</v>
+        <v>248.4663587570968</v>
       </c>
       <c r="T14" t="n">
-        <v>343.2180339898704</v>
+        <v>342.2180339898704</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>386.8510241668239</v>
+        <v>385.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>395.3734759809475</v>
+        <v>239.1304052876834</v>
       </c>
       <c r="X14" t="n">
-        <v>349.2818334606677</v>
+        <v>348.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>268.3174326828064</v>
+        <v>267.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>141.5565566463266</v>
+        <v>140.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>118.0999124455193</v>
+        <v>117.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>104.9376868977026</v>
+        <v>103.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>99.67209722191262</v>
+        <v>98.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>96.63624233787687</v>
+        <v>95.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>82.68361134672546</v>
+        <v>81.68361134672546</v>
       </c>
       <c r="H15" t="n">
-        <v>88.62797397887397</v>
+        <v>87.62797397887397</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>300.801570877285</v>
+        <v>299.801570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>222.5252263797056</v>
+        <v>221.5252263797056</v>
       </c>
       <c r="T15" t="n">
-        <v>162.1323501231742</v>
+        <v>161.1323501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>157.2066805149037</v>
+        <v>156.2066805149037</v>
       </c>
       <c r="V15" t="n">
-        <v>171.5106671915202</v>
+        <v>170.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>189.3731429098285</v>
+        <v>188.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>176.8627394453875</v>
+        <v>175.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>156.3913927661343</v>
+        <v>155.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1760,22 +1760,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>44.11380033707866</v>
+        <v>43.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>29.72524664804467</v>
+        <v>28.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>42.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>37.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>31.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.996987595628392</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1808,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>114.4084907739156</v>
+        <v>240.1661572297981</v>
       </c>
       <c r="S16" t="n">
-        <v>118.5563977356423</v>
+        <v>117.5563977356423</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.443645430107551</v>
+        <v>3.443645430107551</v>
       </c>
       <c r="Y16" t="n">
-        <v>44.46535284946236</v>
+        <v>43.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1851,7 +1851,7 @@
         <v>120.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>120.7465035105114</v>
+        <v>120.8896287080119</v>
       </c>
       <c r="G17" t="n">
         <v>119.6528496739509</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>208.4663587570968</v>
+        <v>208.3232335595965</v>
       </c>
       <c r="T17" t="n">
         <v>302.2180339898704</v>
@@ -2030,22 +2030,22 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>128.7931519746268</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>280.0103539602095</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>397.7773399512283</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>437.913266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>440.4939968336101</v>
+        <v>13.60689639162019</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>119.6528496739509</v>
       </c>
       <c r="H23" t="n">
-        <v>122.9392164924721</v>
+        <v>122.9392164924722</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>208.3232335595965</v>
+        <v>208.4663587570968</v>
       </c>
       <c r="T23" t="n">
         <v>302.2180339898704</v>
       </c>
       <c r="U23" t="n">
-        <v>365.2129347395655</v>
+        <v>365.2129347395654</v>
       </c>
       <c r="V23" t="n">
-        <v>345.8510241668239</v>
+        <v>345.7078989693235</v>
       </c>
       <c r="W23" t="n">
         <v>354.3734759809475</v>
@@ -2410,7 +2410,7 @@
         <v>41.68361134672546</v>
       </c>
       <c r="H24" t="n">
-        <v>47.62797397887396</v>
+        <v>47.62797397887397</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>259.801570877285</v>
+        <v>259.8015708772849</v>
       </c>
       <c r="S24" t="n">
-        <v>181.5252263797056</v>
+        <v>181.5252263797057</v>
       </c>
       <c r="T24" t="n">
         <v>121.1323501231742</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>397.7773399512283</v>
       </c>
       <c r="Q25" t="n">
-        <v>408.8035059348363</v>
+        <v>437.913266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>440.4939968336101</v>
+        <v>13.60689639162025</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>175.8336834439518</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>228.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>189.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>183.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>185.9392164924722</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>365.2180339898704</v>
+        <v>294.8383735333754</v>
       </c>
       <c r="U26" t="n">
-        <v>428.2129347395655</v>
+        <v>428.2129347395654</v>
       </c>
       <c r="V26" t="n">
         <v>408.8510241668239</v>
@@ -2619,7 +2619,7 @@
         <v>371.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>290.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>322.801570877285</v>
+        <v>322.8015708772849</v>
       </c>
       <c r="S27" t="n">
-        <v>244.5252263797056</v>
+        <v>244.5252263797057</v>
       </c>
       <c r="T27" t="n">
         <v>184.1323501231742</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7.354273642602227</v>
+        <v>7.354273642602237</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>260.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>31.86362598689247</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>185.9392164924721</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>23.31288023532966</v>
       </c>
       <c r="S29" t="n">
-        <v>271.4663587570968</v>
+        <v>223.7924887566103</v>
       </c>
       <c r="T29" t="n">
         <v>365.2180339898704</v>
       </c>
       <c r="U29" t="n">
-        <v>428.2129347395654</v>
+        <v>428.2129347395655</v>
       </c>
       <c r="V29" t="n">
         <v>408.8510241668239</v>
@@ -2853,7 +2853,7 @@
         <v>417.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>371.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>290.3174326828064</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>322.8015708772849</v>
+        <v>322.801570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>244.5252263797057</v>
+        <v>244.5252263797056</v>
       </c>
       <c r="T30" t="n">
         <v>184.1323501231742</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7.354273642602237</v>
+        <v>7.354273642602227</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2984,19 +2984,19 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>318.4212312688555</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>111.3994806837509</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>140.5563977356423</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>66.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3030,16 +3030,16 @@
         <v>179.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>140.3391557398498</v>
+        <v>2.821815023653733</v>
       </c>
       <c r="E32" t="n">
-        <v>134.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>134.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>133.6528496739509</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3048,37 +3048,37 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>267.8670435282805</v>
+        <v>266.8670435283078</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>22.27435614227558</v>
       </c>
       <c r="L32" t="n">
-        <v>526.3229151060871</v>
+        <v>654.5055477386934</v>
       </c>
       <c r="M32" t="n">
-        <v>672</v>
+        <v>136.6378258106051</v>
       </c>
       <c r="N32" t="n">
-        <v>33.93530442526844</v>
+        <v>32.93530442529573</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="P32" t="n">
-        <v>657.2565776286212</v>
+        <v>656.2565776286485</v>
       </c>
       <c r="Q32" t="n">
-        <v>377.1262610685252</v>
+        <v>216.6833447262808</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>222.4663587570968</v>
       </c>
       <c r="T32" t="n">
-        <v>2.142084041938952</v>
+        <v>316.2180339898704</v>
       </c>
       <c r="U32" t="n">
         <v>379.2129347395655</v>
@@ -3185,13 +3185,13 @@
         <v>17.11380033707866</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.725246648044674</v>
       </c>
       <c r="D34" t="n">
         <v>15.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>10.98090483695654</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>105.2959699902608</v>
+        <v>84.42568306109216</v>
       </c>
       <c r="R34" t="n">
         <v>454.4939968336101</v>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>211.9993129555745</v>
+        <v>123.7036400557992</v>
       </c>
       <c r="C35" t="n">
-        <v>179.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3276,37 +3276,37 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>133.6528496739509</v>
       </c>
       <c r="H35" t="n">
-        <v>6.702615023653735</v>
+        <v>136.9392164924722</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>267.8670435282804</v>
+        <v>266.8670435283205</v>
       </c>
       <c r="K35" t="n">
-        <v>658.7043316582915</v>
+        <v>40.46623819619105</v>
       </c>
       <c r="L35" t="n">
-        <v>526.3229151060731</v>
+        <v>654.5055477386934</v>
       </c>
       <c r="M35" t="n">
-        <v>137.6378258105779</v>
+        <v>136.6378258106179</v>
       </c>
       <c r="N35" t="n">
-        <v>33.93530442526844</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="O35" t="n">
-        <v>35.10075887340281</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="P35" t="n">
-        <v>657.2565776286211</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>217.6833447262534</v>
+        <v>216.6833447262935</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>316.2180339898704</v>
       </c>
       <c r="U35" t="n">
-        <v>379.2129347395655</v>
+        <v>379.2129347395654</v>
       </c>
       <c r="V35" t="n">
         <v>359.8510241668239</v>
@@ -3358,7 +3358,7 @@
         <v>55.68361134672546</v>
       </c>
       <c r="H36" t="n">
-        <v>61.62797397887396</v>
+        <v>61.62797397887397</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>273.801570877285</v>
+        <v>273.8015708772849</v>
       </c>
       <c r="S36" t="n">
-        <v>195.5252263797056</v>
+        <v>195.5252263797057</v>
       </c>
       <c r="T36" t="n">
         <v>135.1323501231742</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>146.57707078073</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>243.2821359927138</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>294.0103539602095</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3464,13 +3464,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>451.913266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>242.3843339318586</v>
       </c>
       <c r="S37" t="n">
-        <v>17.59217506795639</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>179.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>140.3391557398498</v>
+        <v>2.821815023653733</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3516,46 +3516,46 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>88.82981804090009</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>267.8670435282804</v>
+        <v>266.8670435283178</v>
       </c>
       <c r="K38" t="n">
-        <v>21.80509053169567</v>
+        <v>657.7043316582914</v>
       </c>
       <c r="L38" t="n">
-        <v>526.3229151060087</v>
+        <v>37.26745427662978</v>
       </c>
       <c r="M38" t="n">
-        <v>137.6378258105779</v>
+        <v>136.6378258106151</v>
       </c>
       <c r="N38" t="n">
-        <v>33.93530442526844</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="O38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="P38" t="n">
-        <v>657.2565776286211</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>217.6833447262534</v>
+        <v>216.6833447262908</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>222.4663587570968</v>
       </c>
       <c r="T38" t="n">
         <v>316.2180339898704</v>
       </c>
       <c r="U38" t="n">
-        <v>379.2129347395655</v>
+        <v>379.2129347395654</v>
       </c>
       <c r="V38" t="n">
         <v>359.8510241668239</v>
@@ -3595,7 +3595,7 @@
         <v>55.68361134672546</v>
       </c>
       <c r="H39" t="n">
-        <v>61.62797397887396</v>
+        <v>61.62797397887397</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>273.801570877285</v>
+        <v>273.8015708772849</v>
       </c>
       <c r="S39" t="n">
-        <v>195.5252263797056</v>
+        <v>195.5252263797057</v>
       </c>
       <c r="T39" t="n">
         <v>135.1323501231742</v>
@@ -3686,25 +3686,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>146.57707078073</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>243.2821359927138</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>294.0103539602095</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>17.59217506795639</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>239.8036035238483</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>454.49399683361</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30.22794241860346</v>
+        <v>261.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>229.4745782429939</v>
@@ -3747,13 +3747,13 @@
         <v>184.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>184.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>186.9392164924721</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3789,16 +3789,16 @@
         <v>272.4663587570968</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>366.2180339898704</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>409.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>418.3734759809475</v>
+        <v>224.3047078364697</v>
       </c>
       <c r="X41" t="n">
         <v>372.2818334606677</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>317.6813197944181</v>
+        <v>313.8005197948119</v>
       </c>
       <c r="S42" t="n">
         <v>245.5252263797056</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>67.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>8.354273642602227</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>63.07356068638894</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>302.8326710512516</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>79.23450539151293</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>6.372809838709685</v>
       </c>
       <c r="X43" t="n">
-        <v>27.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>67.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>174.1087011671786</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>251.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>212.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>206.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>206.8896287080119</v>
+        <v>207.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>205.6528496739509</v>
+        <v>206.6528496739509</v>
       </c>
       <c r="H44" t="n">
-        <v>208.9392164924721</v>
+        <v>209.9392164924721</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,28 +4020,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>46.31288023532966</v>
+        <v>47.31288023532966</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>388.2180339898704</v>
+        <v>210.5029565422303</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>452.2129347395655</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>432.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>441.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>394.2818334606677</v>
+        <v>395.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>313.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>186.5565566463266</v>
+        <v>187.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>163.0999124455193</v>
+        <v>164.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>149.9376868977026</v>
+        <v>150.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>144.6720972219126</v>
+        <v>145.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>141.6362423378769</v>
+        <v>142.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>127.6836113467255</v>
+        <v>128.6836113467255</v>
       </c>
       <c r="H45" t="n">
-        <v>133.627973978874</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>17.20091419323533</v>
+        <v>18.20091419323533</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>345.801570877285</v>
+        <v>198.6922437411855</v>
       </c>
       <c r="S45" t="n">
-        <v>267.5252263797057</v>
+        <v>268.5252263797057</v>
       </c>
       <c r="T45" t="n">
-        <v>207.1323501231742</v>
+        <v>208.1323501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>203.2066805149037</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>217.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>165.7809296629348</v>
+        <v>235.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>221.8627394453875</v>
+        <v>222.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>201.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>31.35427364260223</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>85.07356068638894</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -4184,16 +4184,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>11.82423863740526</v>
+        <v>12.82423863740526</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2.170310216216194</v>
       </c>
       <c r="W46" t="n">
-        <v>28.37280983870968</v>
+        <v>29.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1356.184564105199</v>
+        <v>325.4209222538562</v>
       </c>
       <c r="C2" t="n">
-        <v>1306.21024264763</v>
+        <v>275.4466007962866</v>
       </c>
       <c r="D2" t="n">
-        <v>1295.766650991216</v>
+        <v>265.0030091398727</v>
       </c>
       <c r="E2" t="n">
-        <v>887.3188837115505</v>
+        <v>260.5956459006114</v>
       </c>
       <c r="F2" t="n">
-        <v>882.3798648145688</v>
+        <v>255.6566270036298</v>
       </c>
       <c r="G2" t="n">
-        <v>474.6497136287598</v>
+        <v>251.9668798582248</v>
       </c>
       <c r="H2" t="n">
-        <v>63.6</v>
+        <v>211.1268198408925</v>
       </c>
       <c r="I2" t="n">
         <v>63.6</v>
@@ -4324,16 +4324,16 @@
         <v>455.8348045168885</v>
       </c>
       <c r="K2" t="n">
-        <v>454.281575433765</v>
+        <v>453.2844695085132</v>
       </c>
       <c r="L2" t="n">
-        <v>1194.935196693186</v>
+        <v>454.9623352936709</v>
       </c>
       <c r="M2" t="n">
-        <v>1178.954893662883</v>
+        <v>978.7418041718751</v>
       </c>
       <c r="N2" t="n">
-        <v>1162.974590632579</v>
+        <v>1607.271294651402</v>
       </c>
       <c r="O2" t="n">
         <v>1950.024590632579</v>
@@ -4345,28 +4345,28 @@
         <v>3180</v>
       </c>
       <c r="R2" t="n">
-        <v>3180</v>
+        <v>2933.219312893606</v>
       </c>
       <c r="S2" t="n">
-        <v>3062.501784283235</v>
+        <v>2839.818950512701</v>
       </c>
       <c r="T2" t="n">
-        <v>2874.402760051043</v>
+        <v>2651.719926280508</v>
       </c>
       <c r="U2" t="n">
-        <v>2622.672522940371</v>
+        <v>1995.949285129432</v>
       </c>
       <c r="V2" t="n">
-        <v>2390.499771256711</v>
+        <v>1763.776533445772</v>
       </c>
       <c r="W2" t="n">
-        <v>2149.718482387067</v>
+        <v>1118.954840535724</v>
       </c>
       <c r="X2" t="n">
-        <v>1551.454004143968</v>
+        <v>924.7307663330289</v>
       </c>
       <c r="Y2" t="n">
-        <v>1439.012152949214</v>
+        <v>408.2485110978708</v>
       </c>
     </row>
     <row r="3">
@@ -4427,25 +4427,25 @@
         <v>1152.143738371278</v>
       </c>
       <c r="S3" t="n">
-        <v>928.2803329265407</v>
+        <v>1085.95664101804</v>
       </c>
       <c r="T3" t="n">
-        <v>923.0961408829304</v>
+        <v>676.7320449340259</v>
       </c>
       <c r="U3" t="n">
-        <v>922.8873726860579</v>
+        <v>272.4828726967494</v>
       </c>
       <c r="V3" t="n">
-        <v>908.2301330986638</v>
+        <v>116.3635175305213</v>
       </c>
       <c r="W3" t="n">
-        <v>875.5299887453017</v>
+        <v>83.66337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>855.4666155681425</v>
+        <v>63.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>452.0409663094209</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1052.667469848834</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="C4" t="n">
-        <v>1178.66947566727</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="D4" t="n">
-        <v>1291.98861979227</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="E4" t="n">
-        <v>1409.817524003683</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="F4" t="n">
-        <v>1534.178496595618</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="G4" t="n">
-        <v>1534.178496595618</v>
+        <v>2335.761380116958</v>
       </c>
       <c r="H4" t="n">
-        <v>1534.178496595618</v>
+        <v>2505.690649210782</v>
       </c>
       <c r="I4" t="n">
-        <v>1534.178496595618</v>
+        <v>2728.219395687848</v>
       </c>
       <c r="J4" t="n">
-        <v>1534.178496595618</v>
+        <v>3092.584775356693</v>
       </c>
       <c r="K4" t="n">
-        <v>1534.178496595618</v>
+        <v>3180</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.433980655487</v>
+        <v>3163.255484059869</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.007580662847</v>
+        <v>3048.829084067228</v>
       </c>
       <c r="N4" t="n">
-        <v>1237.340556460615</v>
+        <v>2883.162059864997</v>
       </c>
       <c r="O4" t="n">
-        <v>1001.160205263067</v>
+        <v>2646.981708667449</v>
       </c>
       <c r="P4" t="n">
-        <v>716.5366295547556</v>
+        <v>2362.358132959137</v>
       </c>
       <c r="Q4" t="n">
-        <v>391.3717139733435</v>
+        <v>2037.193217377725</v>
       </c>
       <c r="R4" t="n">
-        <v>63.6</v>
+        <v>1709.421503404382</v>
       </c>
       <c r="S4" t="n">
-        <v>63.6</v>
+        <v>1747.480669646096</v>
       </c>
       <c r="T4" t="n">
-        <v>172.9613425584197</v>
+        <v>1935.754673395065</v>
       </c>
       <c r="U4" t="n">
-        <v>419.515066999985</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="V4" t="n">
-        <v>618.3364598859309</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="W4" t="n">
-        <v>790.2273781456083</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="X4" t="n">
-        <v>941.2581691698018</v>
+        <v>2182.30839783663</v>
       </c>
       <c r="Y4" t="n">
-        <v>1052.667469848834</v>
+        <v>2182.30839783663</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>291.5901718248796</v>
+        <v>729.4613262942603</v>
       </c>
       <c r="C5" t="n">
-        <v>241.61585036731</v>
+        <v>679.4870048366906</v>
       </c>
       <c r="D5" t="n">
-        <v>231.1722587108961</v>
+        <v>669.0434131802767</v>
       </c>
       <c r="E5" t="n">
-        <v>226.7648954716348</v>
+        <v>664.6360499410155</v>
       </c>
       <c r="F5" t="n">
-        <v>221.8258765746531</v>
+        <v>255.6566270036298</v>
       </c>
       <c r="G5" t="n">
         <v>218.1361294292482</v>
@@ -4558,22 +4558,22 @@
         <v>63.6</v>
       </c>
       <c r="J5" t="n">
-        <v>63.6</v>
+        <v>455.8348045168885</v>
       </c>
       <c r="K5" t="n">
-        <v>786.1630512432384</v>
+        <v>1178.397855760127</v>
       </c>
       <c r="L5" t="n">
-        <v>1573.213051243238</v>
+        <v>1179.078615620032</v>
       </c>
       <c r="M5" t="n">
-        <v>2096.992520121443</v>
+        <v>1702.858084498237</v>
       </c>
       <c r="N5" t="n">
-        <v>2725.52201060097</v>
+        <v>2331.387574977764</v>
       </c>
       <c r="O5" t="n">
-        <v>2738.162547833207</v>
+        <v>2315.40727194746</v>
       </c>
       <c r="P5" t="n">
         <v>2737.074590632579</v>
@@ -4582,28 +4582,28 @@
         <v>3180</v>
       </c>
       <c r="R5" t="n">
-        <v>3180</v>
+        <v>2933.219312893606</v>
       </c>
       <c r="S5" t="n">
-        <v>3086.599637619094</v>
+        <v>2435.778546472297</v>
       </c>
       <c r="T5" t="n">
-        <v>2494.460209346498</v>
+        <v>2247.679522240104</v>
       </c>
       <c r="U5" t="n">
-        <v>1962.118534700455</v>
+        <v>1995.949285129432</v>
       </c>
       <c r="V5" t="n">
-        <v>1325.905378976391</v>
+        <v>1763.776533445772</v>
       </c>
       <c r="W5" t="n">
-        <v>1085.124090106747</v>
+        <v>1522.995244576128</v>
       </c>
       <c r="X5" t="n">
-        <v>486.8596118636482</v>
+        <v>1328.771170373433</v>
       </c>
       <c r="Y5" t="n">
-        <v>374.4177606688943</v>
+        <v>812.288915138275</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.6</v>
+        <v>415.0522089875785</v>
       </c>
       <c r="C6" t="n">
-        <v>63.6</v>
+        <v>415.0522089875785</v>
       </c>
       <c r="D6" t="n">
         <v>63.6</v>
@@ -4658,31 +4658,31 @@
         <v>1297.397850368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1297.397850368536</v>
+        <v>1129.781135106568</v>
       </c>
       <c r="R6" t="n">
-        <v>1152.143738371278</v>
+        <v>942.4939900086356</v>
       </c>
       <c r="S6" t="n">
-        <v>1085.95664101804</v>
+        <v>876.3068926553975</v>
       </c>
       <c r="T6" t="n">
-        <v>1080.77244897443</v>
+        <v>871.1227006117872</v>
       </c>
       <c r="U6" t="n">
-        <v>1080.563680777558</v>
+        <v>870.9139324149147</v>
       </c>
       <c r="V6" t="n">
-        <v>924.4443256113295</v>
+        <v>856.2566928275206</v>
       </c>
       <c r="W6" t="n">
-        <v>487.7037772175632</v>
+        <v>823.5565484741585</v>
       </c>
       <c r="X6" t="n">
-        <v>63.6</v>
+        <v>803.4931752969993</v>
       </c>
       <c r="Y6" t="n">
-        <v>63.6</v>
+        <v>803.4931752969993</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>383.783971563145</v>
+        <v>797.9623513781642</v>
       </c>
       <c r="C7" t="n">
-        <v>383.783971563145</v>
+        <v>797.9623513781642</v>
       </c>
       <c r="D7" t="n">
-        <v>383.783971563145</v>
+        <v>911.2814955031643</v>
       </c>
       <c r="E7" t="n">
-        <v>383.783971563145</v>
+        <v>1029.110399714577</v>
       </c>
       <c r="F7" t="n">
-        <v>508.1449441550805</v>
+        <v>1153.471372306513</v>
       </c>
       <c r="G7" t="n">
-        <v>661.5979264354083</v>
+        <v>1153.471372306513</v>
       </c>
       <c r="H7" t="n">
-        <v>831.5271955292321</v>
+        <v>1153.471372306513</v>
       </c>
       <c r="I7" t="n">
-        <v>1054.055942006299</v>
+        <v>1169.813116926774</v>
       </c>
       <c r="J7" t="n">
-        <v>1418.421321675143</v>
+        <v>1534.178496595618</v>
       </c>
       <c r="K7" t="n">
         <v>1534.178496595618</v>
@@ -4743,25 +4743,25 @@
         <v>63.6</v>
       </c>
       <c r="S7" t="n">
-        <v>101.6591662417141</v>
+        <v>63.6</v>
       </c>
       <c r="T7" t="n">
-        <v>289.9331699906829</v>
+        <v>251.8740037489688</v>
       </c>
       <c r="U7" t="n">
-        <v>289.9331699906829</v>
+        <v>251.8740037489688</v>
       </c>
       <c r="V7" t="n">
-        <v>289.9331699906829</v>
+        <v>251.8740037489688</v>
       </c>
       <c r="W7" t="n">
-        <v>289.9331699906829</v>
+        <v>423.7649220086462</v>
       </c>
       <c r="X7" t="n">
-        <v>289.9331699906829</v>
+        <v>574.7957130328397</v>
       </c>
       <c r="Y7" t="n">
-        <v>289.9331699906829</v>
+        <v>686.205013711872</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1133.501730334665</v>
+        <v>695.6305758652836</v>
       </c>
       <c r="C8" t="n">
-        <v>1083.527408877095</v>
+        <v>645.656254407714</v>
       </c>
       <c r="D8" t="n">
-        <v>1073.083817220681</v>
+        <v>635.2126627513001</v>
       </c>
       <c r="E8" t="n">
-        <v>1068.67645398142</v>
+        <v>226.7648954716348</v>
       </c>
       <c r="F8" t="n">
-        <v>882.3798648145688</v>
+        <v>221.8258765746531</v>
       </c>
       <c r="G8" t="n">
-        <v>474.6497136287598</v>
+        <v>218.1361294292482</v>
       </c>
       <c r="H8" t="n">
-        <v>63.6</v>
+        <v>211.1268198408925</v>
       </c>
       <c r="I8" t="n">
         <v>63.6</v>
       </c>
       <c r="J8" t="n">
-        <v>63.6</v>
+        <v>455.8348045168885</v>
       </c>
       <c r="K8" t="n">
-        <v>785.1659453179878</v>
+        <v>453.2844695085132</v>
       </c>
       <c r="L8" t="n">
-        <v>1523.10722585373</v>
+        <v>1191.225750044221</v>
       </c>
       <c r="M8" t="n">
-        <v>1507.126922823426</v>
+        <v>1715.005218922425</v>
       </c>
       <c r="N8" t="n">
-        <v>2135.656413302953</v>
+        <v>2343.534709401952</v>
       </c>
       <c r="O8" t="n">
-        <v>2119.67611027265</v>
+        <v>3130.584709401952</v>
       </c>
       <c r="P8" t="n">
-        <v>2906.72611027265</v>
+        <v>3129.496752201324</v>
       </c>
       <c r="Q8" t="n">
         <v>3180</v>
@@ -4822,25 +4822,25 @@
         <v>2933.219312893606</v>
       </c>
       <c r="S8" t="n">
-        <v>2839.818950512701</v>
+        <v>2435.778546472297</v>
       </c>
       <c r="T8" t="n">
-        <v>2651.719926280508</v>
+        <v>2213.848771811127</v>
       </c>
       <c r="U8" t="n">
-        <v>2399.989689169836</v>
+        <v>1962.118534700455</v>
       </c>
       <c r="V8" t="n">
-        <v>2167.816937486176</v>
+        <v>1729.945783016795</v>
       </c>
       <c r="W8" t="n">
-        <v>1927.035648616532</v>
+        <v>1489.164494147151</v>
       </c>
       <c r="X8" t="n">
-        <v>1732.811574413837</v>
+        <v>1294.940419944456</v>
       </c>
       <c r="Y8" t="n">
-        <v>1216.329319178679</v>
+        <v>778.4581647092982</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>428.3473863086054</v>
+        <v>409.7334315372855</v>
       </c>
       <c r="C9" t="n">
-        <v>63.6</v>
+        <v>409.7334315372855</v>
       </c>
       <c r="D9" t="n">
-        <v>63.6</v>
+        <v>409.7334315372855</v>
       </c>
       <c r="E9" t="n">
         <v>63.6</v>
@@ -4907,19 +4907,19 @@
         <v>1080.77244897443</v>
       </c>
       <c r="U9" t="n">
-        <v>1080.563680777558</v>
+        <v>676.5232767371535</v>
       </c>
       <c r="V9" t="n">
-        <v>1065.906441190164</v>
+        <v>661.8660371497594</v>
       </c>
       <c r="W9" t="n">
-        <v>629.1658927963974</v>
+        <v>429.7968047144446</v>
       </c>
       <c r="X9" t="n">
-        <v>609.1025196192383</v>
+        <v>409.7334315372855</v>
       </c>
       <c r="Y9" t="n">
-        <v>428.3473863086054</v>
+        <v>409.7334315372855</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>744.8327713917283</v>
+        <v>847.0656249844865</v>
       </c>
       <c r="C10" t="n">
-        <v>870.8347772101641</v>
+        <v>973.0676308029223</v>
       </c>
       <c r="D10" t="n">
-        <v>927.623240123425</v>
+        <v>1042.439592917749</v>
       </c>
       <c r="E10" t="n">
-        <v>1045.452144334838</v>
+        <v>1042.439592917749</v>
       </c>
       <c r="F10" t="n">
-        <v>1169.813116926774</v>
+        <v>1042.439592917749</v>
       </c>
       <c r="G10" t="n">
-        <v>1169.813116926774</v>
+        <v>1195.892575198077</v>
       </c>
       <c r="H10" t="n">
-        <v>1169.813116926774</v>
+        <v>1195.892575198077</v>
       </c>
       <c r="I10" t="n">
-        <v>1169.813116926774</v>
+        <v>1418.421321675143</v>
       </c>
       <c r="J10" t="n">
-        <v>1534.178496595618</v>
+        <v>1418.421321675143</v>
       </c>
       <c r="K10" t="n">
         <v>1534.178496595618</v>
@@ -4980,25 +4980,25 @@
         <v>63.6</v>
       </c>
       <c r="S10" t="n">
-        <v>63.6</v>
+        <v>101.6591662417141</v>
       </c>
       <c r="T10" t="n">
-        <v>63.6</v>
+        <v>289.9331699906829</v>
       </c>
       <c r="U10" t="n">
-        <v>310.1537244415653</v>
+        <v>536.4868944322483</v>
       </c>
       <c r="V10" t="n">
-        <v>310.1537244415653</v>
+        <v>735.3082873181943</v>
       </c>
       <c r="W10" t="n">
-        <v>482.0446427012428</v>
+        <v>735.3082873181943</v>
       </c>
       <c r="X10" t="n">
-        <v>633.0754337254363</v>
+        <v>735.3082873181943</v>
       </c>
       <c r="Y10" t="n">
-        <v>633.0754337254363</v>
+        <v>735.3082873181943</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>689.3419661535208</v>
+        <v>806.8777621023269</v>
       </c>
       <c r="C11" t="n">
-        <v>458.5595638878704</v>
+        <v>806.8777621023269</v>
       </c>
       <c r="D11" t="n">
-        <v>267.3078914233756</v>
+        <v>806.8777621023269</v>
       </c>
       <c r="E11" t="n">
-        <v>267.3078914233756</v>
+        <v>621.6623180549848</v>
       </c>
       <c r="F11" t="n">
-        <v>267.3078914233756</v>
+        <v>435.9152183499223</v>
       </c>
       <c r="G11" t="n">
         <v>251.4173903964365</v>
@@ -5032,25 +5032,25 @@
         <v>63.6</v>
       </c>
       <c r="J11" t="n">
-        <v>63.6</v>
+        <v>463.6916269070024</v>
       </c>
       <c r="K11" t="n">
-        <v>786.4690780061599</v>
+        <v>1186.560704913162</v>
       </c>
       <c r="L11" t="n">
-        <v>802.7985857448533</v>
+        <v>1973.610704913162</v>
       </c>
       <c r="M11" t="n">
-        <v>1331.817138192381</v>
+        <v>2502.629257360691</v>
       </c>
       <c r="N11" t="n">
-        <v>1963.501186811366</v>
+        <v>2715.630523131326</v>
       </c>
       <c r="O11" t="n">
-        <v>2750.551186811365</v>
+        <v>2715.630523131326</v>
       </c>
       <c r="P11" t="n">
-        <v>2765.147174959031</v>
+        <v>2730.226511278991</v>
       </c>
       <c r="Q11" t="n">
         <v>3180</v>
@@ -5071,13 +5071,13 @@
         <v>1667.816937486176</v>
       </c>
       <c r="W11" t="n">
-        <v>1246.227567808451</v>
+        <v>1667.816937486176</v>
       </c>
       <c r="X11" t="n">
-        <v>1246.227567808451</v>
+        <v>1292.7847824754</v>
       </c>
       <c r="Y11" t="n">
-        <v>952.9776358056164</v>
+        <v>1070.513431754422</v>
       </c>
     </row>
     <row r="12">
@@ -5111,13 +5111,13 @@
         <v>69.34109494869703</v>
       </c>
       <c r="J12" t="n">
-        <v>417.3184202183356</v>
+        <v>217.0111741787275</v>
       </c>
       <c r="K12" t="n">
-        <v>834.2415153693228</v>
+        <v>633.9342693297147</v>
       </c>
       <c r="L12" t="n">
-        <v>1336.403285455089</v>
+        <v>1136.096039415481</v>
       </c>
       <c r="M12" t="n">
         <v>1454.99488115834</v>
@@ -5205,13 +5205,13 @@
         <v>385.2376073422784</v>
       </c>
       <c r="O13" t="n">
-        <v>63.6</v>
+        <v>385.2376073422784</v>
       </c>
       <c r="P13" t="n">
-        <v>63.6</v>
+        <v>385.2376073422784</v>
       </c>
       <c r="Q13" t="n">
-        <v>63.6</v>
+        <v>385.2376073422784</v>
       </c>
       <c r="R13" t="n">
         <v>63.6</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>924.6259068392758</v>
+        <v>1089.517897438533</v>
       </c>
       <c r="C14" t="n">
-        <v>716.0657267958476</v>
+        <v>881.9678184052054</v>
       </c>
       <c r="D14" t="n">
-        <v>547.036276553575</v>
+        <v>713.9484691730339</v>
       </c>
       <c r="E14" t="n">
-        <v>384.0430547284552</v>
+        <v>551.965348358015</v>
       </c>
       <c r="F14" t="n">
-        <v>229.1951681742143</v>
+        <v>389.4505718852758</v>
       </c>
       <c r="G14" t="n">
-        <v>229.1951681742143</v>
+        <v>228.1850671641133</v>
       </c>
       <c r="H14" t="n">
         <v>63.6</v>
@@ -5272,49 +5272,49 @@
         <v>463.6916269070024</v>
       </c>
       <c r="K14" t="n">
-        <v>476.8543385652939</v>
+        <v>1186.560704913162</v>
       </c>
       <c r="L14" t="n">
-        <v>1217.651410785823</v>
+        <v>1202.890212651856</v>
       </c>
       <c r="M14" t="n">
-        <v>1746.669963233351</v>
+        <v>1731.908765099384</v>
       </c>
       <c r="N14" t="n">
-        <v>2378.354011852335</v>
+        <v>2363.592813718368</v>
       </c>
       <c r="O14" t="n">
-        <v>3165.404011852335</v>
+        <v>3150.642813718368</v>
       </c>
       <c r="P14" t="n">
-        <v>3180</v>
+        <v>3165.238801866034</v>
       </c>
       <c r="Q14" t="n">
         <v>3180</v>
       </c>
       <c r="R14" t="n">
-        <v>3178.673858348152</v>
+        <v>3179.683959358253</v>
       </c>
       <c r="S14" t="n">
-        <v>2926.687637381388</v>
+        <v>2928.707839401589</v>
       </c>
       <c r="T14" t="n">
-        <v>2580.002754563337</v>
+        <v>2583.03305759364</v>
       </c>
       <c r="U14" t="n">
-        <v>2580.002754563337</v>
+        <v>2583.03305759364</v>
       </c>
       <c r="V14" t="n">
-        <v>2189.244144293817</v>
+        <v>2193.284548334222</v>
       </c>
       <c r="W14" t="n">
-        <v>1789.876996838315</v>
+        <v>1951.738684407269</v>
       </c>
       <c r="X14" t="n">
-        <v>1437.067064049761</v>
+        <v>1599.938852628816</v>
       </c>
       <c r="Y14" t="n">
-        <v>1166.039354269149</v>
+        <v>1329.921243858305</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>660.2237618470817</v>
+        <v>654.1631557864756</v>
       </c>
       <c r="C15" t="n">
-        <v>540.9309209930218</v>
+        <v>535.8804159425167</v>
       </c>
       <c r="D15" t="n">
-        <v>434.9332574599888</v>
+        <v>430.8928534195848</v>
       </c>
       <c r="E15" t="n">
-        <v>334.2543713772488</v>
+        <v>331.2240683469457</v>
       </c>
       <c r="F15" t="n">
-        <v>236.6420053793934</v>
+        <v>234.6218033591913</v>
       </c>
       <c r="G15" t="n">
-        <v>153.1232060392666</v>
+        <v>152.1131050291656</v>
       </c>
       <c r="H15" t="n">
         <v>63.6</v>
       </c>
       <c r="I15" t="n">
-        <v>83.17051557575542</v>
+        <v>92.11109494869703</v>
       </c>
       <c r="J15" t="n">
-        <v>212.357840845394</v>
+        <v>462.8584202183356</v>
       </c>
       <c r="K15" t="n">
-        <v>410.4909359963812</v>
+        <v>902.5515153693228</v>
       </c>
       <c r="L15" t="n">
-        <v>934.4327060821473</v>
+        <v>1427.483285455089</v>
       </c>
       <c r="M15" t="n">
-        <v>1034.541547825007</v>
+        <v>1769.152127197948</v>
       </c>
       <c r="N15" t="n">
-        <v>1422.791419791065</v>
+        <v>1916.831999164007</v>
       </c>
       <c r="O15" t="n">
-        <v>1915.576680720067</v>
+        <v>2169.047260093009</v>
       </c>
       <c r="P15" t="n">
-        <v>2279.248365944291</v>
+        <v>2292.148945317233</v>
       </c>
       <c r="Q15" t="n">
-        <v>2355.537223316037</v>
+        <v>2340.385708164522</v>
       </c>
       <c r="R15" t="n">
-        <v>2051.697252732921</v>
+        <v>2037.555838591507</v>
       </c>
       <c r="S15" t="n">
-        <v>1826.924296793824</v>
+        <v>1813.792983662511</v>
       </c>
       <c r="T15" t="n">
-        <v>1663.154246164356</v>
+        <v>1651.033034043143</v>
       </c>
       <c r="U15" t="n">
-        <v>1504.359619381624</v>
+        <v>1493.248508270513</v>
       </c>
       <c r="V15" t="n">
-        <v>1331.116521208372</v>
+        <v>1321.015511107362</v>
       </c>
       <c r="W15" t="n">
-        <v>1139.830518269151</v>
+        <v>1130.739609178242</v>
       </c>
       <c r="X15" t="n">
-        <v>961.1812865061332</v>
+        <v>953.100478425325</v>
       </c>
       <c r="Y15" t="n">
-        <v>803.2101827019571</v>
+        <v>796.13947563125</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>208.6729425292193</v>
+        <v>160.447919521361</v>
       </c>
       <c r="C16" t="n">
-        <v>178.6474408645277</v>
+        <v>131.4325188667704</v>
       </c>
       <c r="D16" t="n">
-        <v>135.6815640407342</v>
+        <v>131.4325188667704</v>
       </c>
       <c r="E16" t="n">
-        <v>97.31701370037408</v>
+        <v>131.4325188667704</v>
       </c>
       <c r="F16" t="n">
-        <v>65.61715918750343</v>
+        <v>131.4325188667704</v>
       </c>
       <c r="G16" t="n">
+        <v>131.4325188667704</v>
+      </c>
+      <c r="H16" t="n">
+        <v>146.9217879605942</v>
+      </c>
+      <c r="I16" t="n">
+        <v>215.0105344376607</v>
+      </c>
+      <c r="J16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="K16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="L16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="M16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="N16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="O16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="P16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>424.9359141065055</v>
+      </c>
+      <c r="R16" t="n">
+        <v>182.3438360966084</v>
+      </c>
+      <c r="S16" t="n">
         <v>63.6</v>
       </c>
-      <c r="H16" t="n">
-        <v>78.09926909382379</v>
-      </c>
-      <c r="I16" t="n">
-        <v>145.1980155708903</v>
-      </c>
-      <c r="J16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="K16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="L16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="M16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="N16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="O16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="P16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>354.133395239735</v>
-      </c>
-      <c r="R16" t="n">
-        <v>238.5692631448708</v>
-      </c>
-      <c r="S16" t="n">
-        <v>118.8153260381614</v>
-      </c>
       <c r="T16" t="n">
-        <v>151.6593297871302</v>
+        <v>97.43400374896879</v>
       </c>
       <c r="U16" t="n">
-        <v>242.7830542286955</v>
+        <v>189.5477281905341</v>
       </c>
       <c r="V16" t="n">
-        <v>286.1744471146415</v>
+        <v>233.9291210764801</v>
       </c>
       <c r="W16" t="n">
-        <v>302.6353653743188</v>
+        <v>251.3800393361575</v>
       </c>
       <c r="X16" t="n">
-        <v>298.1468346368364</v>
+        <v>247.9016096087762</v>
       </c>
       <c r="Y16" t="n">
-        <v>253.2323368090967</v>
+        <v>203.9972127911374</v>
       </c>
     </row>
     <row r="17">
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>846.9490841077242</v>
+        <v>847.0936550142903</v>
       </c>
       <c r="C17" t="n">
-        <v>679.8030454784373</v>
+        <v>679.9476163850035</v>
       </c>
       <c r="D17" t="n">
-        <v>552.1877366503062</v>
+        <v>552.3323075568724</v>
       </c>
       <c r="E17" t="n">
-        <v>430.6086562393277</v>
+        <v>430.7532271458939</v>
       </c>
       <c r="F17" t="n">
         <v>308.642491077195</v>
@@ -5509,22 +5509,22 @@
         <v>463.6916269070024</v>
       </c>
       <c r="K17" t="n">
-        <v>476.8543385652939</v>
+        <v>1186.560704913162</v>
       </c>
       <c r="L17" t="n">
-        <v>1263.904338565294</v>
+        <v>1973.610704913162</v>
       </c>
       <c r="M17" t="n">
-        <v>1792.922891012822</v>
+        <v>2502.629257360691</v>
       </c>
       <c r="N17" t="n">
-        <v>2424.606939631806</v>
+        <v>3134.313305979675</v>
       </c>
       <c r="O17" t="n">
-        <v>2715.630523131326</v>
+        <v>3165.404011852335</v>
       </c>
       <c r="P17" t="n">
-        <v>2730.226511278991</v>
+        <v>3180</v>
       </c>
       <c r="Q17" t="n">
         <v>3180</v>
@@ -5533,25 +5533,25 @@
         <v>3180</v>
       </c>
       <c r="S17" t="n">
-        <v>2969.427920447377</v>
+        <v>2969.572491353943</v>
       </c>
       <c r="T17" t="n">
-        <v>2664.157179043467</v>
+        <v>2664.301749950033</v>
       </c>
       <c r="U17" t="n">
-        <v>2295.255224761078</v>
+        <v>2295.399795667644</v>
       </c>
       <c r="V17" t="n">
-        <v>1945.9107559057</v>
+        <v>1946.055326812266</v>
       </c>
       <c r="W17" t="n">
-        <v>1587.957749864339</v>
+        <v>1588.102320770905</v>
       </c>
       <c r="X17" t="n">
-        <v>1276.561958489927</v>
+        <v>1276.706529396493</v>
       </c>
       <c r="Y17" t="n">
-        <v>1046.948390123456</v>
+        <v>1047.092961030022</v>
       </c>
     </row>
     <row r="18">
@@ -5594,13 +5594,13 @@
         <v>742.403285455089</v>
       </c>
       <c r="M18" t="n">
-        <v>842.5121271979482</v>
+        <v>1094.449426612886</v>
       </c>
       <c r="N18" t="n">
-        <v>990.191999164007</v>
+        <v>1242.129298578945</v>
       </c>
       <c r="O18" t="n">
-        <v>1242.407260093009</v>
+        <v>1494.344559507947</v>
       </c>
       <c r="P18" t="n">
         <v>1617.44624473217</v>
@@ -5673,19 +5673,19 @@
         <v>921.4762654226732</v>
       </c>
       <c r="M19" t="n">
-        <v>791.3821725190098</v>
+        <v>921.4762654226732</v>
       </c>
       <c r="N19" t="n">
-        <v>508.5434311450608</v>
+        <v>921.4762654226732</v>
       </c>
       <c r="O19" t="n">
-        <v>508.5434311450608</v>
+        <v>921.4762654226732</v>
       </c>
       <c r="P19" t="n">
-        <v>508.5434311450608</v>
+        <v>519.6809725426447</v>
       </c>
       <c r="Q19" t="n">
-        <v>508.5434311450608</v>
+        <v>77.34433978951535</v>
       </c>
       <c r="R19" t="n">
         <v>63.6</v>
@@ -5746,19 +5746,19 @@
         <v>463.6916269070024</v>
       </c>
       <c r="K20" t="n">
-        <v>1186.560704913162</v>
+        <v>766.1444024737855</v>
       </c>
       <c r="L20" t="n">
-        <v>1202.890212651856</v>
+        <v>782.4739102124788</v>
       </c>
       <c r="M20" t="n">
-        <v>1731.908765099384</v>
+        <v>1311.492462660007</v>
       </c>
       <c r="N20" t="n">
-        <v>2363.592813718368</v>
+        <v>1943.176511278991</v>
       </c>
       <c r="O20" t="n">
-        <v>2715.630523131326</v>
+        <v>1943.176511278991</v>
       </c>
       <c r="P20" t="n">
         <v>2730.226511278991</v>
@@ -5983,16 +5983,16 @@
         <v>63.6</v>
       </c>
       <c r="K23" t="n">
-        <v>767.8779220648136</v>
+        <v>786.4690780061599</v>
       </c>
       <c r="L23" t="n">
-        <v>1554.927922064813</v>
+        <v>802.7985857448533</v>
       </c>
       <c r="M23" t="n">
-        <v>2083.946474512341</v>
+        <v>1331.817138192381</v>
       </c>
       <c r="N23" t="n">
-        <v>2715.630523131326</v>
+        <v>1963.501186811366</v>
       </c>
       <c r="O23" t="n">
         <v>2715.630523131326</v>
@@ -6007,13 +6007,13 @@
         <v>3180</v>
       </c>
       <c r="S23" t="n">
-        <v>2969.572491353943</v>
+        <v>2969.427920447377</v>
       </c>
       <c r="T23" t="n">
-        <v>2664.301749950033</v>
+        <v>2664.157179043467</v>
       </c>
       <c r="U23" t="n">
-        <v>2295.399795667644</v>
+        <v>2295.255224761078</v>
       </c>
       <c r="V23" t="n">
         <v>1946.055326812266</v>
@@ -6114,22 +6114,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>445.970830360351</v>
+        <v>445.9708303603511</v>
       </c>
       <c r="C25" t="n">
-        <v>457.1328361787868</v>
+        <v>457.1328361787869</v>
       </c>
       <c r="D25" t="n">
-        <v>457.1328361787868</v>
+        <v>457.1328361787869</v>
       </c>
       <c r="E25" t="n">
-        <v>460.1217403901998</v>
+        <v>460.1217403901999</v>
       </c>
       <c r="F25" t="n">
-        <v>469.6427129821353</v>
+        <v>469.6427129821354</v>
       </c>
       <c r="G25" t="n">
-        <v>508.2556952624632</v>
+        <v>508.2556952624633</v>
       </c>
       <c r="H25" t="n">
         <v>563.3449643562871</v>
@@ -6156,10 +6156,10 @@
         <v>921.4762654226732</v>
       </c>
       <c r="P25" t="n">
-        <v>921.4762654226732</v>
+        <v>519.6809725426447</v>
       </c>
       <c r="Q25" t="n">
-        <v>508.5434311450608</v>
+        <v>77.3443397895154</v>
       </c>
       <c r="R25" t="n">
         <v>63.6</v>
@@ -6171,19 +6171,19 @@
         <v>137.0340037489688</v>
       </c>
       <c r="U25" t="n">
-        <v>268.7477281905341</v>
+        <v>268.7477281905342</v>
       </c>
       <c r="V25" t="n">
-        <v>352.7291210764801</v>
+        <v>352.7291210764802</v>
       </c>
       <c r="W25" t="n">
-        <v>409.7800393361575</v>
+        <v>409.7800393361576</v>
       </c>
       <c r="X25" t="n">
-        <v>445.970830360351</v>
+        <v>445.9708303603511</v>
       </c>
       <c r="Y25" t="n">
-        <v>445.970830360351</v>
+        <v>445.9708303603511</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>475.7940747301452</v>
+        <v>427.244490101499</v>
       </c>
       <c r="C26" t="n">
-        <v>245.0116724644948</v>
+        <v>427.244490101499</v>
       </c>
       <c r="D26" t="n">
-        <v>53.76</v>
+        <v>427.244490101499</v>
       </c>
       <c r="E26" t="n">
-        <v>53.76</v>
+        <v>427.244490101499</v>
       </c>
       <c r="F26" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="G26" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="H26" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I26" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J26" t="n">
-        <v>368.1557026678286</v>
+        <v>53.68</v>
       </c>
       <c r="K26" t="n">
-        <v>381.3184143261201</v>
+        <v>66.84271165829146</v>
       </c>
       <c r="L26" t="n">
-        <v>397.6479220648135</v>
+        <v>731.1327116582914</v>
       </c>
       <c r="M26" t="n">
-        <v>926.6664745123416</v>
+        <v>1260.151264105819</v>
       </c>
       <c r="N26" t="n">
-        <v>1558.350523131326</v>
+        <v>1891.835312724804</v>
       </c>
       <c r="O26" t="n">
-        <v>2223.630523131326</v>
+        <v>2219.630523131326</v>
       </c>
       <c r="P26" t="n">
-        <v>2238.226511278991</v>
+        <v>2234.226511278991</v>
       </c>
       <c r="Q26" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R26" t="n">
-        <v>2664.45163612593</v>
+        <v>2660.45163612593</v>
       </c>
       <c r="S26" t="n">
-        <v>2664.45163612593</v>
+        <v>2660.45163612593</v>
       </c>
       <c r="T26" t="n">
-        <v>2295.544531085657</v>
+        <v>2362.635097203328</v>
       </c>
       <c r="U26" t="n">
-        <v>1863.006213166904</v>
+        <v>1930.096779284575</v>
       </c>
       <c r="V26" t="n">
-        <v>1450.025380675163</v>
+        <v>1517.115946792834</v>
       </c>
       <c r="W26" t="n">
-        <v>1028.436010997438</v>
+        <v>1095.526577115109</v>
       </c>
       <c r="X26" t="n">
-        <v>653.4038559866622</v>
+        <v>720.4944221043338</v>
       </c>
       <c r="Y26" t="n">
-        <v>653.4038559866622</v>
+        <v>427.244490101499</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>783.717095180415</v>
+        <v>783.637095180415</v>
       </c>
       <c r="C27" t="n">
-        <v>642.2020321041329</v>
+        <v>642.1220321041329</v>
       </c>
       <c r="D27" t="n">
-        <v>513.9821463488777</v>
+        <v>513.9021463488777</v>
       </c>
       <c r="E27" t="n">
-        <v>391.0810380439154</v>
+        <v>391.0010380439155</v>
       </c>
       <c r="F27" t="n">
-        <v>271.2464498238378</v>
+        <v>271.1664498238378</v>
       </c>
       <c r="G27" t="n">
-        <v>165.5054282614889</v>
+        <v>165.4254282614889</v>
       </c>
       <c r="H27" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I27" t="n">
-        <v>59.50109494869702</v>
+        <v>59.42109494869702</v>
       </c>
       <c r="J27" t="n">
-        <v>407.4784202183356</v>
+        <v>407.3984202183356</v>
       </c>
       <c r="K27" t="n">
-        <v>824.4015153693229</v>
+        <v>824.3215153693228</v>
       </c>
       <c r="L27" t="n">
-        <v>1326.563285455089</v>
+        <v>1326.483285455089</v>
       </c>
       <c r="M27" t="n">
-        <v>1645.462127197948</v>
+        <v>1645.382127197948</v>
       </c>
       <c r="N27" t="n">
-        <v>1811.624753124399</v>
+        <v>1811.544753124399</v>
       </c>
       <c r="O27" t="n">
-        <v>2282.630014053401</v>
+        <v>2282.550014053401</v>
       </c>
       <c r="P27" t="n">
-        <v>2624.521699277625</v>
+        <v>2624.441699277625</v>
       </c>
       <c r="Q27" t="n">
-        <v>2679.03055664937</v>
+        <v>2678.95055664937</v>
       </c>
       <c r="R27" t="n">
-        <v>2352.968363844032</v>
+        <v>2352.888363844032</v>
       </c>
       <c r="S27" t="n">
-        <v>2105.973185682713</v>
+        <v>2105.893185682713</v>
       </c>
       <c r="T27" t="n">
-        <v>1919.980912831022</v>
+        <v>1919.900912831022</v>
       </c>
       <c r="U27" t="n">
-        <v>1738.964063826068</v>
+        <v>1738.884063826069</v>
       </c>
       <c r="V27" t="n">
-        <v>1543.498743430594</v>
+        <v>1543.418743430594</v>
       </c>
       <c r="W27" t="n">
-        <v>1329.990518269151</v>
+        <v>1329.910518269151</v>
       </c>
       <c r="X27" t="n">
-        <v>1129.119064283911</v>
+        <v>1129.039064283911</v>
       </c>
       <c r="Y27" t="n">
-        <v>948.9257382575125</v>
+        <v>948.8457382575126</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="C28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="D28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="E28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="F28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="G28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="H28" t="n">
-        <v>142.923481196367</v>
+        <v>142.843481196367</v>
       </c>
       <c r="I28" t="n">
-        <v>188.2422276734336</v>
+        <v>188.1622276734336</v>
       </c>
       <c r="J28" t="n">
-        <v>375.3976073422783</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="K28" t="n">
-        <v>375.3976073422783</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="L28" t="n">
-        <v>375.3976073422783</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="M28" t="n">
-        <v>375.3976073422783</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="N28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="O28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="P28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="R28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="S28" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="T28" t="n">
-        <v>64.82400374896879</v>
+        <v>64.74400374896881</v>
       </c>
       <c r="U28" t="n">
-        <v>134.1677281905341</v>
+        <v>134.0877281905341</v>
       </c>
       <c r="V28" t="n">
-        <v>155.7791210764801</v>
+        <v>155.6991210764801</v>
       </c>
       <c r="W28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="X28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="Y28" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>85.94548079484088</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="C29" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="D29" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="E29" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="F29" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="G29" t="n">
-        <v>53.76</v>
+        <v>241.4973903964365</v>
       </c>
       <c r="H29" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I29" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J29" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="K29" t="n">
-        <v>66.92271165829145</v>
+        <v>717.9699999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>397.6479220648135</v>
+        <v>734.2995077386934</v>
       </c>
       <c r="M29" t="n">
-        <v>926.6664745123416</v>
+        <v>1263.318060186221</v>
       </c>
       <c r="N29" t="n">
-        <v>1558.350523131326</v>
+        <v>1895.002108805206</v>
       </c>
       <c r="O29" t="n">
-        <v>2223.630523131326</v>
+        <v>2219.630523131326</v>
       </c>
       <c r="P29" t="n">
-        <v>2238.226511278991</v>
+        <v>2234.226511278991</v>
       </c>
       <c r="Q29" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R29" t="n">
-        <v>2664.45163612593</v>
+        <v>2660.45163612593</v>
       </c>
       <c r="S29" t="n">
-        <v>2390.243192936943</v>
+        <v>2434.398617179859</v>
       </c>
       <c r="T29" t="n">
-        <v>2021.33608789667</v>
+        <v>2065.491512139586</v>
       </c>
       <c r="U29" t="n">
-        <v>1588.797769977917</v>
+        <v>1632.953194220833</v>
       </c>
       <c r="V29" t="n">
-        <v>1175.816937486176</v>
+        <v>1219.972361729092</v>
       </c>
       <c r="W29" t="n">
-        <v>754.2275678084511</v>
+        <v>798.3829920513667</v>
       </c>
       <c r="X29" t="n">
-        <v>379.1954127976756</v>
+        <v>798.3829920513667</v>
       </c>
       <c r="Y29" t="n">
-        <v>85.94548079484088</v>
+        <v>505.133060048532</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>783.717095180415</v>
+        <v>783.637095180415</v>
       </c>
       <c r="C30" t="n">
-        <v>642.2020321041329</v>
+        <v>642.1220321041329</v>
       </c>
       <c r="D30" t="n">
-        <v>513.9821463488777</v>
+        <v>513.9021463488777</v>
       </c>
       <c r="E30" t="n">
-        <v>391.0810380439154</v>
+        <v>391.0010380439155</v>
       </c>
       <c r="F30" t="n">
-        <v>271.2464498238378</v>
+        <v>271.1664498238378</v>
       </c>
       <c r="G30" t="n">
-        <v>165.5054282614889</v>
+        <v>165.4254282614889</v>
       </c>
       <c r="H30" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I30" t="n">
-        <v>59.50109494869702</v>
+        <v>59.42109494869703</v>
       </c>
       <c r="J30" t="n">
-        <v>407.4784202183356</v>
+        <v>407.3984202183356</v>
       </c>
       <c r="K30" t="n">
-        <v>824.4015153693229</v>
+        <v>824.3215153693228</v>
       </c>
       <c r="L30" t="n">
-        <v>1126.256039415481</v>
+        <v>1326.483285455089</v>
       </c>
       <c r="M30" t="n">
-        <v>1445.15488115834</v>
+        <v>1645.382127197948</v>
       </c>
       <c r="N30" t="n">
-        <v>1811.624753124399</v>
+        <v>1811.544753124399</v>
       </c>
       <c r="O30" t="n">
-        <v>2282.630014053401</v>
+        <v>2282.550014053401</v>
       </c>
       <c r="P30" t="n">
-        <v>2624.521699277625</v>
+        <v>2624.441699277625</v>
       </c>
       <c r="Q30" t="n">
-        <v>2679.03055664937</v>
+        <v>2678.95055664937</v>
       </c>
       <c r="R30" t="n">
-        <v>2352.968363844032</v>
+        <v>2352.888363844032</v>
       </c>
       <c r="S30" t="n">
-        <v>2105.973185682713</v>
+        <v>2105.893185682713</v>
       </c>
       <c r="T30" t="n">
-        <v>1919.980912831022</v>
+        <v>1919.900912831022</v>
       </c>
       <c r="U30" t="n">
-        <v>1738.964063826068</v>
+        <v>1738.884063826069</v>
       </c>
       <c r="V30" t="n">
-        <v>1543.498743430594</v>
+        <v>1543.418743430594</v>
       </c>
       <c r="W30" t="n">
-        <v>1329.990518269151</v>
+        <v>1329.910518269151</v>
       </c>
       <c r="X30" t="n">
-        <v>1129.119064283911</v>
+        <v>1129.039064283911</v>
       </c>
       <c r="Y30" t="n">
-        <v>948.9257382575125</v>
+        <v>948.8457382575126</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="C31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="D31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="E31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="F31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="G31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="H31" t="n">
-        <v>75.78676114640507</v>
+        <v>142.843481196367</v>
       </c>
       <c r="I31" t="n">
-        <v>121.1055076234716</v>
+        <v>188.1622276734336</v>
       </c>
       <c r="J31" t="n">
-        <v>308.2608872923163</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="K31" t="n">
-        <v>308.2608872923163</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="L31" t="n">
-        <v>308.2608872923163</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="M31" t="n">
-        <v>308.2608872923163</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="N31" t="n">
-        <v>308.2608872923163</v>
+        <v>375.3176073422783</v>
       </c>
       <c r="O31" t="n">
-        <v>308.2608872923163</v>
+        <v>53.68</v>
       </c>
       <c r="P31" t="n">
-        <v>308.2608872923163</v>
+        <v>53.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>195.7361593289316</v>
+        <v>53.68</v>
       </c>
       <c r="R31" t="n">
-        <v>195.7361593289316</v>
+        <v>53.68</v>
       </c>
       <c r="S31" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="T31" t="n">
-        <v>64.82400374896881</v>
+        <v>64.74400374896879</v>
       </c>
       <c r="U31" t="n">
-        <v>134.1677281905341</v>
+        <v>134.0877281905341</v>
       </c>
       <c r="V31" t="n">
-        <v>155.7791210764801</v>
+        <v>155.6991210764801</v>
       </c>
       <c r="W31" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="X31" t="n">
-        <v>150.3520404313188</v>
+        <v>150.2720404313188</v>
       </c>
       <c r="Y31" t="n">
-        <v>83.21532038135682</v>
+        <v>150.2720404313188</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>783.7796989612881</v>
+        <v>237.8177709764118</v>
       </c>
       <c r="C32" t="n">
-        <v>602.4922461905871</v>
+        <v>56.53031820571084</v>
       </c>
       <c r="D32" t="n">
-        <v>460.7355232210418</v>
+        <v>53.68</v>
       </c>
       <c r="E32" t="n">
-        <v>325.0150286686493</v>
+        <v>53.68</v>
       </c>
       <c r="F32" t="n">
-        <v>188.7628784585362</v>
+        <v>53.68</v>
       </c>
       <c r="G32" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="H32" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I32" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J32" t="n">
-        <v>448.4672287593127</v>
+        <v>448.4073297694132</v>
       </c>
       <c r="K32" t="n">
-        <v>1113.747228759313</v>
+        <v>1090.197980130751</v>
       </c>
       <c r="L32" t="n">
-        <v>1119.497114265066</v>
+        <v>1093.371265243182</v>
       </c>
       <c r="M32" t="n">
-        <v>1105.989235477187</v>
+        <v>1619.643259373911</v>
       </c>
       <c r="N32" t="n">
-        <v>1736.991150199138</v>
+        <v>2250.665275105963</v>
       </c>
       <c r="O32" t="n">
-        <v>2402.271150199138</v>
+        <v>2237.177497328157</v>
       </c>
       <c r="P32" t="n">
-        <v>2403.655617240935</v>
+        <v>2238.582065380054</v>
       </c>
       <c r="Q32" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R32" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="S32" t="n">
-        <v>2688</v>
+        <v>2459.286506305963</v>
       </c>
       <c r="T32" t="n">
-        <v>2685.836278745516</v>
+        <v>2139.87435076064</v>
       </c>
       <c r="U32" t="n">
-        <v>2302.792910321712</v>
+        <v>1756.830982336836</v>
       </c>
       <c r="V32" t="n">
-        <v>1939.307027324921</v>
+        <v>1393.345099340044</v>
       </c>
       <c r="W32" t="n">
-        <v>1567.212607142145</v>
+        <v>1021.250679157269</v>
       </c>
       <c r="X32" t="n">
-        <v>1241.675401626319</v>
+        <v>695.713473641443</v>
       </c>
       <c r="Y32" t="n">
-        <v>997.9204191184341</v>
+        <v>451.9584911335577</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>486.7473982107181</v>
+        <v>486.667398210718</v>
       </c>
       <c r="C33" t="n">
-        <v>394.7272846293855</v>
+        <v>394.6472846293854</v>
       </c>
       <c r="D33" t="n">
-        <v>316.0023483690798</v>
+        <v>315.9223483690797</v>
       </c>
       <c r="E33" t="n">
-        <v>242.596189559067</v>
+        <v>242.516189559067</v>
       </c>
       <c r="F33" t="n">
-        <v>172.2565508339388</v>
+        <v>172.1765508339388</v>
       </c>
       <c r="G33" t="n">
-        <v>116.0104787665394</v>
+        <v>115.9304787665394</v>
       </c>
       <c r="H33" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I33" t="n">
-        <v>108.011094948697</v>
+        <v>53.68</v>
       </c>
       <c r="J33" t="n">
-        <v>504.4984202183356</v>
+        <v>182.8673252696386</v>
       </c>
       <c r="K33" t="n">
-        <v>927.1100269054721</v>
+        <v>648.3004204206259</v>
       </c>
       <c r="L33" t="n">
-        <v>1210.481796991238</v>
+        <v>931.6721905063921</v>
       </c>
       <c r="M33" t="n">
-        <v>1310.590638734098</v>
+        <v>1031.781032249251</v>
       </c>
       <c r="N33" t="n">
-        <v>1458.270510700157</v>
+        <v>1190.890510700156</v>
       </c>
       <c r="O33" t="n">
-        <v>1710.485771629159</v>
+        <v>1443.105771629158</v>
       </c>
       <c r="P33" t="n">
-        <v>1833.587456853382</v>
+        <v>1833.507456853382</v>
       </c>
       <c r="Q33" t="n">
-        <v>1936.606314225128</v>
+        <v>1936.526314225128</v>
       </c>
       <c r="R33" t="n">
-        <v>1660.039070914739</v>
+        <v>1659.959070914739</v>
       </c>
       <c r="S33" t="n">
-        <v>1462.53884224837</v>
+        <v>1462.45884224837</v>
       </c>
       <c r="T33" t="n">
-        <v>1326.041518891628</v>
+        <v>1325.961518891628</v>
       </c>
       <c r="U33" t="n">
-        <v>1194.519619381625</v>
+        <v>1194.439619381624</v>
       </c>
       <c r="V33" t="n">
-        <v>1048.549248481099</v>
+        <v>1048.469248481099</v>
       </c>
       <c r="W33" t="n">
-        <v>884.5359728146055</v>
+        <v>884.4559728146054</v>
       </c>
       <c r="X33" t="n">
-        <v>733.1594683243151</v>
+        <v>733.0794683243149</v>
       </c>
       <c r="Y33" t="n">
-        <v>602.4610917928662</v>
+        <v>602.3810917928661</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>331.9023927981883</v>
+        <v>331.8223927981883</v>
       </c>
       <c r="C34" t="n">
-        <v>331.9023927981883</v>
+        <v>329.069618406224</v>
       </c>
       <c r="D34" t="n">
-        <v>316.2092432471222</v>
+        <v>313.3764688551579</v>
       </c>
       <c r="E34" t="n">
-        <v>316.2092432471222</v>
+        <v>302.2846457875251</v>
       </c>
       <c r="F34" t="n">
-        <v>316.2092432471222</v>
+        <v>302.2846457875251</v>
       </c>
       <c r="G34" t="n">
-        <v>340.9622255274501</v>
+        <v>319.801127619199</v>
       </c>
       <c r="H34" t="n">
-        <v>382.1914946212739</v>
+        <v>361.0303967130228</v>
       </c>
       <c r="I34" t="n">
-        <v>476.0202410983404</v>
+        <v>454.8591431900893</v>
       </c>
       <c r="J34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="K34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="L34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="M34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="N34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="O34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="P34" t="n">
-        <v>711.6856207671851</v>
+        <v>690.524522858934</v>
       </c>
       <c r="Q34" t="n">
-        <v>605.326055120457</v>
+        <v>605.2460551204571</v>
       </c>
       <c r="R34" t="n">
-        <v>146.2412098339821</v>
+        <v>146.1612098339822</v>
       </c>
       <c r="S34" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="T34" t="n">
-        <v>113.3340037489688</v>
+        <v>113.2540037489688</v>
       </c>
       <c r="U34" t="n">
-        <v>231.1877281905341</v>
+        <v>231.1077281905341</v>
       </c>
       <c r="V34" t="n">
-        <v>301.3091210764801</v>
+        <v>301.2291210764801</v>
       </c>
       <c r="W34" t="n">
-        <v>344.5000393361575</v>
+        <v>344.4200393361575</v>
       </c>
       <c r="X34" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="Y34" t="n">
-        <v>349.1890598053385</v>
+        <v>349.1090598053385</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241.8177709764118</v>
+        <v>327.0053193600232</v>
       </c>
       <c r="C35" t="n">
-        <v>60.53031820571084</v>
+        <v>327.0053193600232</v>
       </c>
       <c r="D35" t="n">
-        <v>60.53031820571084</v>
+        <v>327.0053193600232</v>
       </c>
       <c r="E35" t="n">
-        <v>60.53031820571084</v>
+        <v>327.0053193600232</v>
       </c>
       <c r="F35" t="n">
-        <v>60.53031820571084</v>
+        <v>327.0053193600232</v>
       </c>
       <c r="G35" t="n">
-        <v>60.53031820571084</v>
+        <v>192.002440901487</v>
       </c>
       <c r="H35" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I35" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J35" t="n">
-        <v>448.4672287593127</v>
+        <v>448.4073297694129</v>
       </c>
       <c r="K35" t="n">
-        <v>448.3893179933617</v>
+        <v>1071.822341692452</v>
       </c>
       <c r="L35" t="n">
-        <v>454.1392034991148</v>
+        <v>1074.995626804883</v>
       </c>
       <c r="M35" t="n">
-        <v>980.3910966197433</v>
+        <v>1601.267620935612</v>
       </c>
       <c r="N35" t="n">
-        <v>1611.393011341694</v>
+        <v>1587.779843157793</v>
       </c>
       <c r="O35" t="n">
-        <v>2241.217699348358</v>
+        <v>1574.292065380015</v>
       </c>
       <c r="P35" t="n">
-        <v>2242.602166390155</v>
+        <v>2238.582065380055</v>
       </c>
       <c r="Q35" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R35" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="S35" t="n">
-        <v>2463.286506305963</v>
+        <v>2459.286506305963</v>
       </c>
       <c r="T35" t="n">
-        <v>2143.87435076064</v>
+        <v>2139.87435076064</v>
       </c>
       <c r="U35" t="n">
-        <v>1760.830982336836</v>
+        <v>1756.830982336836</v>
       </c>
       <c r="V35" t="n">
-        <v>1397.345099340044</v>
+        <v>1393.345099340044</v>
       </c>
       <c r="W35" t="n">
-        <v>1025.250679157269</v>
+        <v>1021.250679157269</v>
       </c>
       <c r="X35" t="n">
-        <v>699.713473641443</v>
+        <v>695.713473641443</v>
       </c>
       <c r="Y35" t="n">
-        <v>455.9584911335577</v>
+        <v>451.9584911335577</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>486.7473982107181</v>
+        <v>486.667398210718</v>
       </c>
       <c r="C36" t="n">
-        <v>394.7272846293855</v>
+        <v>394.6472846293854</v>
       </c>
       <c r="D36" t="n">
-        <v>316.0023483690798</v>
+        <v>315.9223483690797</v>
       </c>
       <c r="E36" t="n">
-        <v>242.596189559067</v>
+        <v>242.516189559067</v>
       </c>
       <c r="F36" t="n">
-        <v>172.2565508339388</v>
+        <v>172.1765508339388</v>
       </c>
       <c r="G36" t="n">
-        <v>116.0104787665394</v>
+        <v>115.9304787665394</v>
       </c>
       <c r="H36" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I36" t="n">
-        <v>108.011094948697</v>
+        <v>107.931094948697</v>
       </c>
       <c r="J36" t="n">
-        <v>237.1984202183356</v>
+        <v>461.596931754485</v>
       </c>
       <c r="K36" t="n">
-        <v>435.3315153693227</v>
+        <v>659.7300269054722</v>
       </c>
       <c r="L36" t="n">
-        <v>718.7032854550889</v>
+        <v>943.1017969912383</v>
       </c>
       <c r="M36" t="n">
-        <v>818.8121271979481</v>
+        <v>1043.210638734098</v>
       </c>
       <c r="N36" t="n">
-        <v>1190.970510700157</v>
+        <v>1190.890510700156</v>
       </c>
       <c r="O36" t="n">
-        <v>1443.185771629159</v>
+        <v>1443.105771629158</v>
       </c>
       <c r="P36" t="n">
-        <v>1833.587456853382</v>
+        <v>1833.507456853382</v>
       </c>
       <c r="Q36" t="n">
-        <v>1936.606314225128</v>
+        <v>1936.526314225128</v>
       </c>
       <c r="R36" t="n">
-        <v>1660.039070914739</v>
+        <v>1659.959070914739</v>
       </c>
       <c r="S36" t="n">
-        <v>1462.53884224837</v>
+        <v>1462.45884224837</v>
       </c>
       <c r="T36" t="n">
-        <v>1326.041518891628</v>
+        <v>1325.961518891628</v>
       </c>
       <c r="U36" t="n">
-        <v>1194.519619381625</v>
+        <v>1194.439619381624</v>
       </c>
       <c r="V36" t="n">
-        <v>1048.549248481099</v>
+        <v>1048.469248481099</v>
       </c>
       <c r="W36" t="n">
-        <v>884.5359728146055</v>
+        <v>884.4559728146054</v>
       </c>
       <c r="X36" t="n">
-        <v>733.1594683243151</v>
+        <v>733.0794683243149</v>
       </c>
       <c r="Y36" t="n">
-        <v>602.4610917928662</v>
+        <v>602.3810917928661</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="C37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="D37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="E37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="F37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="G37" t="n">
-        <v>391.5838126406789</v>
+        <v>384.2673121920394</v>
       </c>
       <c r="H37" t="n">
-        <v>432.8130817345027</v>
+        <v>425.4965812858632</v>
       </c>
       <c r="I37" t="n">
-        <v>526.6418282115692</v>
+        <v>519.3253277629296</v>
       </c>
       <c r="J37" t="n">
-        <v>762.3072078804139</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="K37" t="n">
-        <v>762.3072078804139</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="L37" t="n">
-        <v>614.2495606271513</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="M37" t="n">
-        <v>368.5100293213797</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="N37" t="n">
-        <v>71.52987380601655</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="O37" t="n">
-        <v>71.52987380601655</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="P37" t="n">
-        <v>71.52987380601655</v>
+        <v>754.9907074317744</v>
       </c>
       <c r="Q37" t="n">
-        <v>71.52987380601655</v>
+        <v>298.5126605372309</v>
       </c>
       <c r="R37" t="n">
-        <v>71.52987380601655</v>
+        <v>53.68</v>
       </c>
       <c r="S37" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="T37" t="n">
-        <v>113.3340037489688</v>
+        <v>113.2540037489688</v>
       </c>
       <c r="U37" t="n">
-        <v>231.1877281905341</v>
+        <v>231.1077281905341</v>
       </c>
       <c r="V37" t="n">
-        <v>301.3091210764801</v>
+        <v>301.2291210764801</v>
       </c>
       <c r="W37" t="n">
-        <v>344.5000393361575</v>
+        <v>344.4200393361575</v>
       </c>
       <c r="X37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="Y37" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>466.5312646704483</v>
+        <v>237.8177709764118</v>
       </c>
       <c r="C38" t="n">
-        <v>285.2438118997474</v>
+        <v>56.53031820571084</v>
       </c>
       <c r="D38" t="n">
-        <v>143.4870889302021</v>
+        <v>53.68</v>
       </c>
       <c r="E38" t="n">
-        <v>143.4870889302021</v>
+        <v>53.68</v>
       </c>
       <c r="F38" t="n">
-        <v>143.4870889302021</v>
+        <v>53.68</v>
       </c>
       <c r="G38" t="n">
-        <v>143.4870889302021</v>
+        <v>53.68</v>
       </c>
       <c r="H38" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I38" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J38" t="n">
-        <v>448.4672287593127</v>
+        <v>448.407329769413</v>
       </c>
       <c r="K38" t="n">
-        <v>1091.721884787903</v>
+        <v>448.3495200135629</v>
       </c>
       <c r="L38" t="n">
-        <v>1097.471770293658</v>
+        <v>1074.995626804846</v>
       </c>
       <c r="M38" t="n">
-        <v>1623.723663414286</v>
+        <v>1601.267620935575</v>
       </c>
       <c r="N38" t="n">
-        <v>2254.725578136237</v>
+        <v>1587.779843157796</v>
       </c>
       <c r="O38" t="n">
-        <v>2241.217699348358</v>
+        <v>1574.292065380018</v>
       </c>
       <c r="P38" t="n">
-        <v>2242.602166390155</v>
+        <v>2238.582065380055</v>
       </c>
       <c r="Q38" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R38" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="S38" t="n">
-        <v>2688</v>
+        <v>2459.286506305963</v>
       </c>
       <c r="T38" t="n">
-        <v>2368.587844454676</v>
+        <v>2139.87435076064</v>
       </c>
       <c r="U38" t="n">
-        <v>1985.544476030873</v>
+        <v>1756.830982336836</v>
       </c>
       <c r="V38" t="n">
-        <v>1622.058593034081</v>
+        <v>1393.345099340044</v>
       </c>
       <c r="W38" t="n">
-        <v>1249.964172851305</v>
+        <v>1021.250679157269</v>
       </c>
       <c r="X38" t="n">
-        <v>924.4269673354795</v>
+        <v>695.713473641443</v>
       </c>
       <c r="Y38" t="n">
-        <v>680.6719848275943</v>
+        <v>451.9584911335577</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>486.7473982107181</v>
+        <v>486.667398210718</v>
       </c>
       <c r="C39" t="n">
-        <v>394.7272846293855</v>
+        <v>394.6472846293854</v>
       </c>
       <c r="D39" t="n">
-        <v>316.0023483690798</v>
+        <v>315.9223483690797</v>
       </c>
       <c r="E39" t="n">
-        <v>242.596189559067</v>
+        <v>242.516189559067</v>
       </c>
       <c r="F39" t="n">
-        <v>172.2565508339388</v>
+        <v>172.1765508339388</v>
       </c>
       <c r="G39" t="n">
-        <v>116.0104787665394</v>
+        <v>115.9304787665394</v>
       </c>
       <c r="H39" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I39" t="n">
-        <v>108.011094948697</v>
+        <v>53.68</v>
       </c>
       <c r="J39" t="n">
-        <v>237.1984202183356</v>
+        <v>194.296931754485</v>
       </c>
       <c r="K39" t="n">
-        <v>435.3315153693227</v>
+        <v>659.7300269054722</v>
       </c>
       <c r="L39" t="n">
-        <v>986.0032854550889</v>
+        <v>943.1017969912383</v>
       </c>
       <c r="M39" t="n">
-        <v>1086.112127197948</v>
+        <v>1043.210638734098</v>
       </c>
       <c r="N39" t="n">
-        <v>1233.791999164007</v>
+        <v>1190.890510700156</v>
       </c>
       <c r="O39" t="n">
-        <v>1486.007260093009</v>
+        <v>1710.405771629158</v>
       </c>
       <c r="P39" t="n">
-        <v>1833.587456853382</v>
+        <v>1833.507456853382</v>
       </c>
       <c r="Q39" t="n">
-        <v>1936.606314225128</v>
+        <v>1936.526314225128</v>
       </c>
       <c r="R39" t="n">
-        <v>1660.039070914739</v>
+        <v>1659.959070914739</v>
       </c>
       <c r="S39" t="n">
-        <v>1462.53884224837</v>
+        <v>1462.45884224837</v>
       </c>
       <c r="T39" t="n">
-        <v>1326.041518891628</v>
+        <v>1325.961518891628</v>
       </c>
       <c r="U39" t="n">
-        <v>1194.519619381625</v>
+        <v>1194.439619381624</v>
       </c>
       <c r="V39" t="n">
-        <v>1048.549248481099</v>
+        <v>1048.469248481099</v>
       </c>
       <c r="W39" t="n">
-        <v>884.5359728146055</v>
+        <v>884.4559728146054</v>
       </c>
       <c r="X39" t="n">
-        <v>733.1594683243151</v>
+        <v>733.0794683243149</v>
       </c>
       <c r="Y39" t="n">
-        <v>602.4610917928662</v>
+        <v>602.3810917928661</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="C40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="D40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="E40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="F40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="G40" t="n">
-        <v>391.5838126406789</v>
+        <v>384.2673121920412</v>
       </c>
       <c r="H40" t="n">
-        <v>432.8130817345027</v>
+        <v>425.496581285865</v>
       </c>
       <c r="I40" t="n">
-        <v>526.6418282115692</v>
+        <v>519.3253277629315</v>
       </c>
       <c r="J40" t="n">
-        <v>762.3072078804139</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="K40" t="n">
-        <v>762.3072078804139</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="L40" t="n">
-        <v>614.2495606271513</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="M40" t="n">
-        <v>368.5100293213797</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="N40" t="n">
-        <v>71.52987380601655</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="O40" t="n">
-        <v>53.76</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="P40" t="n">
-        <v>53.76</v>
+        <v>754.9907074317762</v>
       </c>
       <c r="Q40" t="n">
-        <v>53.76</v>
+        <v>512.7648452864748</v>
       </c>
       <c r="R40" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="S40" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="T40" t="n">
-        <v>113.3340037489688</v>
+        <v>113.2540037489688</v>
       </c>
       <c r="U40" t="n">
-        <v>231.1877281905341</v>
+        <v>231.1077281905341</v>
       </c>
       <c r="V40" t="n">
-        <v>301.3091210764801</v>
+        <v>301.2291210764801</v>
       </c>
       <c r="W40" t="n">
-        <v>344.5000393361575</v>
+        <v>344.4200393361575</v>
       </c>
       <c r="X40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
       <c r="Y40" t="n">
-        <v>366.830830360351</v>
+        <v>366.750830360351</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>850.7970225229537</v>
+        <v>852.7873132143278</v>
       </c>
       <c r="C41" t="n">
-        <v>619.0045192472023</v>
+        <v>620.9948099385764</v>
       </c>
       <c r="D41" t="n">
-        <v>426.7427457726066</v>
+        <v>428.7330364639806</v>
       </c>
       <c r="E41" t="n">
-        <v>240.5172007151635</v>
+        <v>242.5074914065375</v>
       </c>
       <c r="F41" t="n">
-        <v>53.76</v>
+        <v>242.5074914065375</v>
       </c>
       <c r="G41" t="n">
-        <v>53.76</v>
+        <v>242.5074914065375</v>
       </c>
       <c r="H41" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I41" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J41" t="n">
-        <v>384.4852104065221</v>
+        <v>453.7716269070024</v>
       </c>
       <c r="K41" t="n">
-        <v>397.6479220648135</v>
+        <v>466.9343385652939</v>
       </c>
       <c r="L41" t="n">
-        <v>1062.927922064813</v>
+        <v>1131.224338565294</v>
       </c>
       <c r="M41" t="n">
-        <v>1591.946474512341</v>
+        <v>1660.242891012822</v>
       </c>
       <c r="N41" t="n">
-        <v>2223.630523131326</v>
+        <v>2219.630523131326</v>
       </c>
       <c r="O41" t="n">
-        <v>2223.630523131326</v>
+        <v>2219.630523131326</v>
       </c>
       <c r="P41" t="n">
-        <v>2238.226511278991</v>
+        <v>2234.226511278991</v>
       </c>
       <c r="Q41" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R41" t="n">
-        <v>2663.441535115829</v>
+        <v>2659.441535115829</v>
       </c>
       <c r="S41" t="n">
-        <v>2388.222990916741</v>
+        <v>2384.222990916741</v>
       </c>
       <c r="T41" t="n">
-        <v>2388.222990916741</v>
+        <v>2014.305784866367</v>
       </c>
       <c r="U41" t="n">
-        <v>2388.222990916741</v>
+        <v>2014.305784866367</v>
       </c>
       <c r="V41" t="n">
-        <v>1974.232057414898</v>
+        <v>2014.305784866367</v>
       </c>
       <c r="W41" t="n">
-        <v>1551.632586727073</v>
+        <v>1787.735372910337</v>
       </c>
       <c r="X41" t="n">
-        <v>1175.590330706196</v>
+        <v>1411.69311688946</v>
       </c>
       <c r="Y41" t="n">
-        <v>881.3302976932603</v>
+        <v>1117.433083876524</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>789.7777012410212</v>
+        <v>789.6977012410212</v>
       </c>
       <c r="C42" t="n">
-        <v>647.252537154638</v>
+        <v>647.172537154638</v>
       </c>
       <c r="D42" t="n">
-        <v>518.0225503892818</v>
+        <v>517.9425503892818</v>
       </c>
       <c r="E42" t="n">
-        <v>394.1113410742186</v>
+        <v>394.0313410742185</v>
       </c>
       <c r="F42" t="n">
-        <v>273.2666518440399</v>
+        <v>273.1866518440398</v>
       </c>
       <c r="G42" t="n">
-        <v>166.5155292715899</v>
+        <v>166.4355292715899</v>
       </c>
       <c r="H42" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I42" t="n">
-        <v>58.51109494869703</v>
+        <v>58.43109494869703</v>
       </c>
       <c r="J42" t="n">
-        <v>405.4984202183356</v>
+        <v>405.4184202183356</v>
       </c>
       <c r="K42" t="n">
-        <v>821.4315153693228</v>
+        <v>635.0037126807522</v>
       </c>
       <c r="L42" t="n">
-        <v>1322.603285455089</v>
+        <v>1136.175482766518</v>
       </c>
       <c r="M42" t="n">
-        <v>1640.512127197948</v>
+        <v>1454.084324509378</v>
       </c>
       <c r="N42" t="n">
-        <v>1877.083053846784</v>
+        <v>1819.564196475437</v>
       </c>
       <c r="O42" t="n">
-        <v>2347.098314775786</v>
+        <v>2289.579457404438</v>
       </c>
       <c r="P42" t="n">
-        <v>2688.00000000001</v>
+        <v>2630.481142628662</v>
       </c>
       <c r="Q42" t="n">
-        <v>2688.00000000001</v>
+        <v>2684.000000000408</v>
       </c>
       <c r="R42" t="n">
-        <v>2367.109777985446</v>
+        <v>2367.029777985446</v>
       </c>
       <c r="S42" t="n">
-        <v>2119.104498814027</v>
+        <v>2119.024498814027</v>
       </c>
       <c r="T42" t="n">
-        <v>1932.102124952234</v>
+        <v>1932.022124952234</v>
       </c>
       <c r="U42" t="n">
-        <v>1750.07517493718</v>
+        <v>1749.99517493718</v>
       </c>
       <c r="V42" t="n">
-        <v>1553.599753531604</v>
+        <v>1553.519753531604</v>
       </c>
       <c r="W42" t="n">
-        <v>1339.08142736006</v>
+        <v>1339.00142736006</v>
       </c>
       <c r="X42" t="n">
-        <v>1137.199872364719</v>
+        <v>1137.119872364719</v>
       </c>
       <c r="Y42" t="n">
-        <v>955.9964453282198</v>
+        <v>955.9164453282198</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="C43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="D43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="E43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="F43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="G43" t="n">
-        <v>53.76</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="H43" t="n">
-        <v>53.76</v>
+        <v>137.853279176165</v>
       </c>
       <c r="I43" t="n">
-        <v>82.38759474281673</v>
+        <v>173.4062072516114</v>
       </c>
       <c r="J43" t="n">
-        <v>268.5529744116615</v>
+        <v>359.5715869204561</v>
       </c>
       <c r="K43" t="n">
-        <v>204.8423070516726</v>
+        <v>359.5715869204561</v>
       </c>
       <c r="L43" t="n">
-        <v>204.8423070516726</v>
+        <v>359.5715869204561</v>
       </c>
       <c r="M43" t="n">
-        <v>204.8423070516726</v>
+        <v>359.5715869204561</v>
       </c>
       <c r="N43" t="n">
-        <v>204.8423070516726</v>
+        <v>53.68</v>
       </c>
       <c r="O43" t="n">
-        <v>204.8423070516726</v>
+        <v>53.68</v>
       </c>
       <c r="P43" t="n">
-        <v>204.8423070516726</v>
+        <v>53.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>204.8423070516726</v>
+        <v>53.68</v>
       </c>
       <c r="R43" t="n">
-        <v>204.8423070516726</v>
+        <v>53.68</v>
       </c>
       <c r="S43" t="n">
-        <v>124.8074531208515</v>
+        <v>53.68</v>
       </c>
       <c r="T43" t="n">
-        <v>134.8814568698203</v>
+        <v>63.7540037489688</v>
       </c>
       <c r="U43" t="n">
-        <v>203.2351813113856</v>
+        <v>132.1077281905341</v>
       </c>
       <c r="V43" t="n">
-        <v>223.8565741973316</v>
+        <v>152.7291210764801</v>
       </c>
       <c r="W43" t="n">
-        <v>217.4193925420693</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="X43" t="n">
-        <v>189.6985385722637</v>
+        <v>146.2919394212178</v>
       </c>
       <c r="Y43" t="n">
-        <v>121.5517175122007</v>
+        <v>146.2919394212178</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1358.465776226411</v>
+        <v>684.4695907822576</v>
       </c>
       <c r="C44" t="n">
-        <v>1104.451050728438</v>
+        <v>684.4695907822576</v>
       </c>
       <c r="D44" t="n">
-        <v>889.9670550316198</v>
+        <v>684.4695907822576</v>
       </c>
       <c r="E44" t="n">
-        <v>681.5192877519545</v>
+        <v>684.4695907822576</v>
       </c>
       <c r="F44" t="n">
-        <v>472.5398648145688</v>
+        <v>474.4800668347708</v>
       </c>
       <c r="G44" t="n">
-        <v>264.8097136287598</v>
+        <v>265.7398146388608</v>
       </c>
       <c r="H44" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I44" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J44" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="K44" t="n">
-        <v>395.9144024737852</v>
+        <v>717.9699999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>412.2439102124787</v>
+        <v>734.2995077386934</v>
       </c>
       <c r="M44" t="n">
-        <v>941.2624626600067</v>
+        <v>1263.318060186221</v>
       </c>
       <c r="N44" t="n">
-        <v>1572.946511278991</v>
+        <v>1895.002108805206</v>
       </c>
       <c r="O44" t="n">
-        <v>1572.946511278991</v>
+        <v>2559.29210880528</v>
       </c>
       <c r="P44" t="n">
-        <v>2238.226511278991</v>
+        <v>2684</v>
       </c>
       <c r="Q44" t="n">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="R44" t="n">
-        <v>2641.219312893606</v>
+        <v>2636.209211883505</v>
       </c>
       <c r="S44" t="n">
-        <v>2641.219312893606</v>
+        <v>2636.209211883505</v>
       </c>
       <c r="T44" t="n">
-        <v>2249.07988462101</v>
+        <v>2423.579962850949</v>
       </c>
       <c r="U44" t="n">
-        <v>2249.07988462101</v>
+        <v>1966.799220689772</v>
       </c>
       <c r="V44" t="n">
-        <v>2249.07988462101</v>
+        <v>1529.575963955606</v>
       </c>
       <c r="W44" t="n">
-        <v>2249.07988462101</v>
+        <v>1083.744170035457</v>
       </c>
       <c r="X44" t="n">
-        <v>1850.815406377911</v>
+        <v>684.4695907822576</v>
       </c>
       <c r="Y44" t="n">
-        <v>1534.333151142753</v>
+        <v>684.4695907822576</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>940.4856953756021</v>
+        <v>811.4885499423962</v>
       </c>
       <c r="C45" t="n">
-        <v>775.7383090669967</v>
+        <v>645.7310626236898</v>
       </c>
       <c r="D45" t="n">
-        <v>624.2861000794184</v>
+        <v>493.2687526260104</v>
       </c>
       <c r="E45" t="n">
-        <v>478.1526685421329</v>
+        <v>346.1252200786239</v>
       </c>
       <c r="F45" t="n">
-        <v>335.0857570897321</v>
+        <v>202.048207616122</v>
       </c>
       <c r="G45" t="n">
-        <v>206.1124122950599</v>
+        <v>72.06476181134882</v>
       </c>
       <c r="H45" t="n">
-        <v>71.1346608012478</v>
+        <v>72.06476181134882</v>
       </c>
       <c r="I45" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J45" t="n">
-        <v>378.9673252696385</v>
+        <v>377.8973252696386</v>
       </c>
       <c r="K45" t="n">
-        <v>773.1204204206257</v>
+        <v>658.5664110591362</v>
       </c>
       <c r="L45" t="n">
-        <v>1252.512190506392</v>
+        <v>1136.968181144902</v>
       </c>
       <c r="M45" t="n">
-        <v>1548.641032249251</v>
+        <v>1432.107022887762</v>
       </c>
       <c r="N45" t="n">
-        <v>1892.34090421531</v>
+        <v>1774.81689485382</v>
       </c>
       <c r="O45" t="n">
-        <v>2340.576165144312</v>
+        <v>2222.062155782823</v>
       </c>
       <c r="P45" t="n">
-        <v>2520.919328812895</v>
+        <v>2540.193841007046</v>
       </c>
       <c r="Q45" t="n">
-        <v>2552.658186184641</v>
+        <v>2570.942698378792</v>
       </c>
       <c r="R45" t="n">
-        <v>2203.363670146979</v>
+        <v>2370.243462276585</v>
       </c>
       <c r="S45" t="n">
-        <v>1933.136168753337</v>
+        <v>2099.005859872841</v>
       </c>
       <c r="T45" t="n">
-        <v>1723.911572669323</v>
+        <v>1888.771162778726</v>
       </c>
       <c r="U45" t="n">
-        <v>1723.911572669323</v>
+        <v>1683.511889531349</v>
       </c>
       <c r="V45" t="n">
-        <v>1723.911572669323</v>
+        <v>1463.80414489345</v>
       </c>
       <c r="W45" t="n">
-        <v>1556.456088161308</v>
+        <v>1226.053495489582</v>
       </c>
       <c r="X45" t="n">
-        <v>1332.352310943744</v>
+        <v>1000.939617261918</v>
       </c>
       <c r="Y45" t="n">
-        <v>1128.926661685023</v>
+        <v>1000.939617261918</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="C46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="D46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="E46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="F46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="G46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="H46" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="I46" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="J46" t="n">
-        <v>180.295968851014</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="K46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="L46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="M46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="N46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="O46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="P46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="Q46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="R46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="S46" t="n">
-        <v>94.36307926880296</v>
+        <v>130.1664973080135</v>
       </c>
       <c r="T46" t="n">
-        <v>82.41940387748453</v>
+        <v>117.2127209065941</v>
       </c>
       <c r="U46" t="n">
-        <v>82.41940387748453</v>
+        <v>117.2127209065941</v>
       </c>
       <c r="V46" t="n">
-        <v>82.41940387748453</v>
+        <v>115.0204883649615</v>
       </c>
       <c r="W46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="X46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
       <c r="Y46" t="n">
-        <v>53.76</v>
+        <v>85.35098347737599</v>
       </c>
     </row>
   </sheetData>
@@ -7970,16 +7970,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>732.5731327855201</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>525.9088713609102</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>458.5987269140563</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>847.6369851519819</v>
+        <v>407.7832481733476</v>
       </c>
       <c r="P2" t="n">
         <v>780.2565776286211</v>
@@ -8201,13 +8201,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>41.99228011443705</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>778.5055477386935</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
@@ -8216,10 +8216,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>80.97161701189667</v>
+        <v>52.63698515198187</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>418.527723126889</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>41.99228011443705</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>728.9007806030789</v>
+        <v>728.900780603045</v>
       </c>
       <c r="M8" t="n">
-        <v>525.9088713609102</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>52.63698515198187</v>
+        <v>847.6369851519819</v>
       </c>
       <c r="P8" t="n">
-        <v>780.2565776286211</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>447.8970688259037</v>
+        <v>227.3541333165159</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>26.17178011443706</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>778.5055477386934</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>673.7515206217687</v>
       </c>
       <c r="O11" t="n">
-        <v>847.6369851519819</v>
+        <v>52.6369851519819</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>580.578675612968</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,10 +8915,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>731.7854186685205</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>161.5354179958271</v>
+        <v>176.4457191412478</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,10 +9152,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>778.5055477386936</v>
+        <v>778.5055477386934</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>346.6002008080624</v>
+        <v>84.04173855870894</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>161.5354179958271</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,7 +9389,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>292.2121857661531</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9401,10 +9401,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>408.2306310236563</v>
+        <v>52.6369851519819</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>780.2565776286211</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,10 +9626,10 @@
         <v>26.17178011443706</v>
       </c>
       <c r="K23" t="n">
-        <v>698.0961721278002</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>778.5055477386934</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,7 +9638,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>52.6369851519819</v>
+        <v>812.3635874953761</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>343.7431969506276</v>
+        <v>26.17178011443706</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>654.5055477386935</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,7 +9875,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>724.6369851519819</v>
+        <v>383.743258289883</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -10100,10 +10100,10 @@
         <v>26.17178011443706</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>657.7043316582915</v>
       </c>
       <c r="L29" t="n">
-        <v>317.5714168361906</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,7 +10112,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>724.6369851519819</v>
+        <v>380.544474370285</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -10337,25 +10337,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>658.7043316582915</v>
+        <v>635.4299755160158</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>525.9088713609102</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>724.6369851519819</v>
+        <v>52.63698515195447</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>456.409156927302</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>617.2380934621004</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,13 +10583,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>458.5987269140162</v>
       </c>
       <c r="O35" t="n">
-        <v>689.5362262785791</v>
+        <v>52.6369851519819</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>656.2565776286613</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,22 +10811,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>636.8992411265957</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>617.2380934620637</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>458.5987269140563</v>
       </c>
       <c r="O38" t="n">
-        <v>52.63698515198187</v>
+        <v>52.6369851519819</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>656.2565776286585</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>360.2376492119341</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>655.5055477386934</v>
+        <v>654.5055477386935</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>1023.636739154969</v>
       </c>
       <c r="O41" t="n">
         <v>52.6369851519819</v>
@@ -11285,7 +11285,7 @@
         <v>26.17178011443706</v>
       </c>
       <c r="K44" t="n">
-        <v>332.3148392075694</v>
+        <v>657.7043316582915</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11297,13 +11297,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>52.6369851519819</v>
+        <v>723.6369851520566</v>
       </c>
       <c r="P44" t="n">
-        <v>657.2565776286211</v>
+        <v>111.2241444919748</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>161.5354179958271</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23226,19 +23226,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>228.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>189.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>183.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>183.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>166.9212536572812</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23286,13 +23286,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>417.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>371.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>70.26879546903814</v>
       </c>
     </row>
     <row r="12">
@@ -23420,7 +23420,7 @@
         <v>343.0103539602095</v>
       </c>
       <c r="O13" t="n">
-        <v>94.39731641671682</v>
+        <v>412.8185476855724</v>
       </c>
       <c r="P13" t="n">
         <v>460.7773399512283</v>
@@ -23429,7 +23429,7 @@
         <v>500.913266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>503.4939968336101</v>
+        <v>185.0727655647545</v>
       </c>
       <c r="S13" t="n">
         <v>140.5563977356423</v>
@@ -23472,10 +23472,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.59022101931339</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>160.6528496739509</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23517,13 +23517,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>406.2129347395655</v>
+        <v>405.2129347395655</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>155.2430706932641</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23624,16 +23624,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>41.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>36.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>30.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.9969875956283925</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,28 +23645,28 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>40.07356068638894</v>
+        <v>39.07356068638894</v>
       </c>
       <c r="L16" t="n">
-        <v>173.57707078073</v>
+        <v>172.57707078073</v>
       </c>
       <c r="M16" t="n">
-        <v>270.2821359927138</v>
+        <v>269.2821359927138</v>
       </c>
       <c r="N16" t="n">
-        <v>321.0103539602095</v>
+        <v>320.0103539602095</v>
       </c>
       <c r="O16" t="n">
-        <v>390.8185476855724</v>
+        <v>389.8185476855724</v>
       </c>
       <c r="P16" t="n">
-        <v>438.7773399512283</v>
+        <v>437.7773399512283</v>
       </c>
       <c r="Q16" t="n">
-        <v>478.913266425598</v>
+        <v>477.913266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>367.0855060596945</v>
+        <v>240.327839603812</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.143125197500467</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1431251975002965</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23888,22 +23888,22 @@
         <v>132.57707078073</v>
       </c>
       <c r="M19" t="n">
-        <v>100.4889840180871</v>
+        <v>229.2821359927138</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>280.0103539602095</v>
       </c>
       <c r="O19" t="n">
         <v>349.8185476855724</v>
       </c>
       <c r="P19" t="n">
-        <v>397.7773399512283</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>437.913266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>426.8871004419899</v>
       </c>
       <c r="S19" t="n">
         <v>77.55639773564232</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1431251975002965</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1431251975003534</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24368,19 +24368,19 @@
         <v>280.0103539602095</v>
       </c>
       <c r="O25" t="n">
-        <v>349.8185476855724</v>
+        <v>349.8185476855723</v>
       </c>
       <c r="P25" t="n">
-        <v>397.7773399512283</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>29.10976049076169</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>426.8871004419898</v>
       </c>
       <c r="S25" t="n">
-        <v>77.55639773564232</v>
+        <v>77.55639773564229</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>85.16562951162274</v>
+        <v>260.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>228.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>189.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>183.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>183.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>182.6528496739509</v>
       </c>
       <c r="H26" t="n">
-        <v>185.9392164924721</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,7 +24462,7 @@
         <v>271.4663587570968</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>70.37966045649495</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>290.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24581,7 +24581,7 @@
         <v>53.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>23.99698759562839</v>
+        <v>23.99698759562838</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>62.07356068638894</v>
+        <v>62.07356068638893</v>
       </c>
       <c r="L28" t="n">
         <v>195.57707078073</v>
@@ -24602,10 +24602,10 @@
         <v>292.2821359927138</v>
       </c>
       <c r="N28" t="n">
-        <v>24.58912269135396</v>
+        <v>24.58912269135402</v>
       </c>
       <c r="O28" t="n">
-        <v>412.8185476855724</v>
+        <v>412.8185476855723</v>
       </c>
       <c r="P28" t="n">
         <v>460.7773399512283</v>
@@ -24614,7 +24614,7 @@
         <v>500.913266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>503.4939968336101</v>
+        <v>503.49399683361</v>
       </c>
       <c r="S28" t="n">
         <v>140.5563977356423</v>
@@ -24645,10 +24645,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>260.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>196.6109522561015</v>
+        <v>228.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>189.3391557398498</v>
@@ -24663,7 +24663,7 @@
         <v>182.6528496739509</v>
       </c>
       <c r="H29" t="n">
-        <v>185.9392164924722</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>47.67387000048649</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24711,7 +24711,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>371.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24818,7 +24818,7 @@
         <v>53.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>23.99698759562838</v>
+        <v>23.99698759562839</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>62.07356068638893</v>
+        <v>62.07356068638894</v>
       </c>
       <c r="L31" t="n">
         <v>195.57707078073</v>
@@ -24842,19 +24842,19 @@
         <v>343.0103539602095</v>
       </c>
       <c r="O31" t="n">
-        <v>412.8185476855723</v>
+        <v>94.39731641671688</v>
       </c>
       <c r="P31" t="n">
         <v>460.7773399512283</v>
       </c>
       <c r="Q31" t="n">
-        <v>389.5137857418471</v>
+        <v>500.913266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>503.49399683361</v>
+        <v>503.4939968336101</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>140.5563977356423</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>26.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>66.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24888,16 +24888,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>137.5173407161961</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>134.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>134.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>133.6528496739509</v>
       </c>
       <c r="H32" t="n">
         <v>136.9392164924721</v>
@@ -24933,10 +24933,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>222.4663587570968</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>314.0759499479315</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -25043,13 +25043,13 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>10.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>4.382855967741932</v>
@@ -25085,7 +25085,7 @@
         <v>411.7773399512283</v>
       </c>
       <c r="Q34" t="n">
-        <v>346.6172964353372</v>
+        <v>367.4875833645058</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25119,10 +25119,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>88.29567289977535</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>179.4745782429939</v>
       </c>
       <c r="D35" t="n">
         <v>140.3391557398498</v>
@@ -25134,10 +25134,10 @@
         <v>134.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>133.6528496739509</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>130.2366014688184</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25304,31 +25304,31 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>13.07356068638894</v>
+        <v>13.07356068638893</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>146.57707078073</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>243.2821359927138</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>294.0103539602095</v>
       </c>
       <c r="O37" t="n">
-        <v>363.8185476855724</v>
+        <v>363.8185476855723</v>
       </c>
       <c r="P37" t="n">
         <v>411.7773399512283</v>
       </c>
       <c r="Q37" t="n">
-        <v>451.913266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>454.4939968336101</v>
+        <v>212.1096629017514</v>
       </c>
       <c r="S37" t="n">
-        <v>73.96422266768593</v>
+        <v>91.55639773564229</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25362,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>137.5173407161961</v>
       </c>
       <c r="E38" t="n">
         <v>134.3632896068686</v>
@@ -25374,7 +25374,7 @@
         <v>133.6528496739509</v>
       </c>
       <c r="H38" t="n">
-        <v>48.10939845157204</v>
+        <v>136.9392164924722</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>222.4663587570968</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25541,31 +25541,31 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>13.07356068638894</v>
+        <v>13.07356068638893</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>146.57707078073</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>243.2821359927138</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>294.0103539602095</v>
       </c>
       <c r="O40" t="n">
-        <v>346.226372617616</v>
+        <v>363.8185476855723</v>
       </c>
       <c r="P40" t="n">
         <v>411.7773399512283</v>
       </c>
       <c r="Q40" t="n">
-        <v>451.913266425598</v>
+        <v>212.1096629017497</v>
       </c>
       <c r="R40" t="n">
-        <v>454.4939968336101</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>91.55639773564232</v>
+        <v>91.55639773564229</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>231.7713705369711</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>184.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>183.6528496739509</v>
       </c>
       <c r="H41" t="n">
-        <v>186.9392164924721</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25647,16 +25647,16 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>366.2180339898704</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>429.2129347395655</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>409.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>194.0687681444778</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6.120251082866901</v>
+        <v>10.00105108247305</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>67.11380033707866</v>
       </c>
       <c r="C43" t="n">
         <v>52.72524664804467</v>
@@ -25769,7 +25769,7 @@
         <v>24.99698759562839</v>
       </c>
       <c r="H43" t="n">
-        <v>8.354273642602227</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25778,7 +25778,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>63.07356068638894</v>
       </c>
       <c r="L43" t="n">
         <v>196.57707078073</v>
@@ -25787,7 +25787,7 @@
         <v>293.2821359927138</v>
       </c>
       <c r="N43" t="n">
-        <v>344.0103539602095</v>
+        <v>41.17768290895793</v>
       </c>
       <c r="O43" t="n">
         <v>413.8185476855724</v>
@@ -25802,7 +25802,7 @@
         <v>504.4939968336101</v>
       </c>
       <c r="S43" t="n">
-        <v>62.3218923441294</v>
+        <v>141.5563977356423</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>27.44364543010755</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>67.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -25830,16 +25830,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>109.8906117883959</v>
+        <v>284.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>252.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>213.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>207.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>294.4663587570968</v>
+        <v>295.4663587570968</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>178.7150774476401</v>
       </c>
       <c r="U44" t="n">
-        <v>451.2129347395655</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>431.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>440.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>314.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25927,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>134.627973978874</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>148.1093271360995</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -25966,19 +25966,19 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>202.2066805149037</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>216.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>68.59221324689372</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>202.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -25988,25 +25988,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>89.11380033707866</v>
+        <v>90.11380033707866</v>
       </c>
       <c r="C46" t="n">
-        <v>74.72524664804467</v>
+        <v>75.72524664804467</v>
       </c>
       <c r="D46" t="n">
-        <v>87.53621805555548</v>
+        <v>88.53621805555548</v>
       </c>
       <c r="E46" t="n">
-        <v>82.98090483695654</v>
+        <v>83.98090483695654</v>
       </c>
       <c r="F46" t="n">
-        <v>76.38285596774193</v>
+        <v>77.38285596774193</v>
       </c>
       <c r="G46" t="n">
-        <v>46.99698759562839</v>
+        <v>47.99698759562839</v>
       </c>
       <c r="H46" t="n">
-        <v>30.35427364260223</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26015,31 +26015,31 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>86.07356068638894</v>
       </c>
       <c r="L46" t="n">
-        <v>218.57707078073</v>
+        <v>219.57707078073</v>
       </c>
       <c r="M46" t="n">
-        <v>315.2821359927138</v>
+        <v>316.2821359927138</v>
       </c>
       <c r="N46" t="n">
-        <v>366.0103539602095</v>
+        <v>367.0103539602095</v>
       </c>
       <c r="O46" t="n">
-        <v>435.8185476855724</v>
+        <v>436.8185476855724</v>
       </c>
       <c r="P46" t="n">
-        <v>483.7773399512283</v>
+        <v>484.7773399512283</v>
       </c>
       <c r="Q46" t="n">
-        <v>523.913266425598</v>
+        <v>524.913266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>526.49399683361</v>
+        <v>527.49399683361</v>
       </c>
       <c r="S46" t="n">
-        <v>163.5563977356423</v>
+        <v>164.5563977356423</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26048,16 +26048,16 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.170310216216194</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>49.44364543010755</v>
+        <v>50.44364543010755</v>
       </c>
       <c r="Y46" t="n">
-        <v>89.46535284946236</v>
+        <v>90.46535284946236</v>
       </c>
     </row>
   </sheetData>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3986796.231106955</v>
+        <v>3987900.391606955</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4751336.056168665</v>
+        <v>4752440.216668664</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5515875.881230374</v>
+        <v>5516980.041730373</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6280415.706292083</v>
+        <v>6281519.866792081</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6937170.202920601</v>
+        <v>6937947.340489285</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7610400.934700633</v>
+        <v>7610985.002469318</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8338188.117548936</v>
+        <v>8338555.901361666</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9064234.38218406</v>
+        <v>9064301.634165127</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9790280.646819189</v>
+        <v>9790047.366968594</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10460270.3541291</v>
+        <v>10459759.7566028</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11093585.54872726</v>
+        <v>11091135.18972596</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1416799.170374169</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="C2" t="n">
         <v>1416799.170374169</v>
@@ -26278,10 +26278,10 @@
         <v>1416799.170374169</v>
       </c>
       <c r="E2" t="n">
-        <v>1254560.970924068</v>
+        <v>1254560.970924067</v>
       </c>
       <c r="F2" t="n">
-        <v>1298292.564986022</v>
+        <v>1300280.053886022</v>
       </c>
       <c r="G2" t="n">
         <v>1376171.685111081</v>
@@ -26293,25 +26293,25 @@
         <v>1376171.685111081</v>
       </c>
       <c r="J2" t="n">
-        <v>1211815.317204067</v>
+        <v>1211467.791564067</v>
       </c>
       <c r="K2" t="n">
-        <v>1211815.317204067</v>
+        <v>1211467.791564067</v>
       </c>
       <c r="L2" t="n">
-        <v>1306883.276343219</v>
+        <v>1306342.319046227</v>
       </c>
       <c r="M2" t="n">
-        <v>1306883.27634322</v>
+        <v>1306342.319046227</v>
       </c>
       <c r="N2" t="n">
-        <v>1306883.27634322</v>
+        <v>1306342.319046228</v>
       </c>
       <c r="O2" t="n">
-        <v>1209115.125941558</v>
+        <v>1208767.600301557</v>
       </c>
       <c r="P2" t="n">
-        <v>1139967.350276679</v>
+        <v>1136475.779621679</v>
       </c>
     </row>
     <row r="3">
@@ -26333,10 +26333,10 @@
         <v>176800</v>
       </c>
       <c r="F3" t="n">
-        <v>17600</v>
+        <v>18400</v>
       </c>
       <c r="G3" t="n">
-        <v>32800</v>
+        <v>32000</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26345,13 +26345,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>362944</v>
+        <v>362592</v>
       </c>
       <c r="K3" t="n">
-        <v>17600</v>
+        <v>18400</v>
       </c>
       <c r="L3" t="n">
-        <v>72000</v>
+        <v>71200</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>646070.2100487291</v>
+        <v>641454.8780939033</v>
       </c>
       <c r="C4" t="n">
-        <v>644317.6901180517</v>
+        <v>639702.3581632259</v>
       </c>
       <c r="D4" t="n">
-        <v>642562.7927847038</v>
+        <v>637947.460829878</v>
       </c>
       <c r="E4" t="n">
-        <v>557091.2953551814</v>
+        <v>552522.9026059485</v>
       </c>
       <c r="F4" t="n">
-        <v>577437.71409448</v>
+        <v>573859.108487769</v>
       </c>
       <c r="G4" t="n">
-        <v>614562.8792296289</v>
+        <v>609994.486480396</v>
       </c>
       <c r="H4" t="n">
-        <v>612881.6784893405</v>
+        <v>608313.2857401075</v>
       </c>
       <c r="I4" t="n">
-        <v>611198.1307655312</v>
+        <v>606629.7380162983</v>
       </c>
       <c r="J4" t="n">
-        <v>533483.1238749273</v>
+        <v>529147.2263078974</v>
       </c>
       <c r="K4" t="n">
-        <v>532044.6844697823</v>
+        <v>527708.7869027521</v>
       </c>
       <c r="L4" t="n">
-        <v>578823.4667259762</v>
+        <v>574449.3517458283</v>
       </c>
       <c r="M4" t="n">
-        <v>577185.0790486829</v>
+        <v>572811.3728279324</v>
       </c>
       <c r="N4" t="n">
-        <v>575544.3356423492</v>
+        <v>571171.0387687241</v>
       </c>
       <c r="O4" t="n">
-        <v>524966.0665690057</v>
+        <v>520630.1690019757</v>
       </c>
       <c r="P4" t="n">
-        <v>490176.3412719234</v>
+        <v>484324.7566602802</v>
       </c>
     </row>
     <row r="5">
@@ -26437,7 +26437,7 @@
         <v>67482.049</v>
       </c>
       <c r="F5" t="n">
-        <v>69331.567</v>
+        <v>69415.636</v>
       </c>
       <c r="G5" t="n">
         <v>72778.39600000001</v>
@@ -26449,25 +26449,25 @@
         <v>72778.39600000001</v>
       </c>
       <c r="J5" t="n">
-        <v>60003.649</v>
+        <v>59942.84899999999</v>
       </c>
       <c r="K5" t="n">
-        <v>60003.649</v>
+        <v>59942.84899999999</v>
       </c>
       <c r="L5" t="n">
-        <v>64123.03</v>
+        <v>64062.23</v>
       </c>
       <c r="M5" t="n">
-        <v>64123.03</v>
+        <v>64062.23</v>
       </c>
       <c r="N5" t="n">
-        <v>64123.03</v>
+        <v>64062.23</v>
       </c>
       <c r="O5" t="n">
-        <v>59919.58</v>
+        <v>59858.78</v>
       </c>
       <c r="P5" t="n">
-        <v>58070.062</v>
+        <v>57925.193</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>383008.5603254399</v>
+        <v>387623.8922802666</v>
       </c>
       <c r="C6" t="n">
-        <v>689951.0802561177</v>
+        <v>694566.4122109433</v>
       </c>
       <c r="D6" t="n">
-        <v>691705.9775894654</v>
+        <v>696321.309544291</v>
       </c>
       <c r="E6" t="n">
-        <v>453187.6265688863</v>
+        <v>457756.0193181188</v>
       </c>
       <c r="F6" t="n">
-        <v>633923.2838915419</v>
+        <v>638605.309398253</v>
       </c>
       <c r="G6" t="n">
-        <v>656030.4098814526</v>
+        <v>661398.8026306853</v>
       </c>
       <c r="H6" t="n">
-        <v>690511.610621741</v>
+        <v>695080.003370974</v>
       </c>
       <c r="I6" t="n">
-        <v>692195.1583455501</v>
+        <v>696763.5510947832</v>
       </c>
       <c r="J6" t="n">
-        <v>255384.5443291402</v>
+        <v>259785.7162561698</v>
       </c>
       <c r="K6" t="n">
-        <v>602166.9837342848</v>
+        <v>605416.1556613152</v>
       </c>
       <c r="L6" t="n">
-        <v>591936.7796172432</v>
+        <v>596630.7373003992</v>
       </c>
       <c r="M6" t="n">
-        <v>665575.167294537</v>
+        <v>669468.7162182952</v>
       </c>
       <c r="N6" t="n">
-        <v>667215.9107008704</v>
+        <v>671109.0502775037</v>
       </c>
       <c r="O6" t="n">
-        <v>537829.4793725519</v>
+        <v>541878.6512995816</v>
       </c>
       <c r="P6" t="n">
-        <v>591720.9470047551</v>
+        <v>594225.8299613992</v>
       </c>
     </row>
   </sheetData>
@@ -26767,7 +26767,7 @@
         <v>221</v>
       </c>
       <c r="F2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G2" t="n">
         <v>284</v>
@@ -26797,7 +26797,7 @@
         <v>220</v>
       </c>
       <c r="P2" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
@@ -26883,25 +26883,25 @@
         <v>795</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="M4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -26984,31 +26984,31 @@
         <v>221</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>158</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>108</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27216,10 +27216,10 @@
         <v>221</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27231,7 +27231,7 @@
         <v>158</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -27442,19 +27442,19 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>366.5075570753132</v>
       </c>
       <c r="I2" t="n">
-        <v>146.0515516424836</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,28 +27481,28 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>244.3128802353297</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>376.1431251974998</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
       </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>400</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27563,16 +27563,16 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>243.9004549894155</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>259.9525055769543</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,31 +27594,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
         <v>400</v>
       </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
         <v>400</v>
       </c>
-      <c r="E4" t="n">
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
         <v>400</v>
       </c>
-      <c r="G4" t="n">
-        <v>244.9969875956284</v>
-      </c>
-      <c r="H4" t="n">
-        <v>228.3542736426022</v>
-      </c>
-      <c r="I4" t="n">
-        <v>175.2234884070035</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.95416195066187</v>
-      </c>
       <c r="K4" t="n">
-        <v>283.0735606863889</v>
+        <v>371.3717673967999</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>361.5563977356423</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>320.2902412216675</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27682,10 +27682,10 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>366.5075570753132</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27718,28 +27718,28 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>244.3128802353297</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>400</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>122.1946768399836</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>165.9405481093475</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>358.3872972303315</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,13 +27809,13 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>259.9525055769543</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>381.9125898042121</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.9969875956284</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.3542736426022</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>191.7303011547418</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>283.0735606863889</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>361.5563977356423</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27916,19 +27916,19 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>400</v>
       </c>
-      <c r="F8" t="n">
-        <v>220.4560054328293</v>
-      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>146.0515516424836</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,10 +27958,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>366.5075570753129</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28043,19 +28043,19 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>202.6246027988669</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>220.4438107886078</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>342.8983018063241</v>
+        <v>355.608907060431</v>
       </c>
       <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
         <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>244.9969875956284</v>
       </c>
       <c r="H10" t="n">
         <v>228.3542736426022</v>
       </c>
       <c r="I10" t="n">
-        <v>175.2234884070035</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
+        <v>31.95416195066187</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="K10" t="n">
-        <v>283.0735606863889</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>361.5563977356423</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.8242386374052</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28247,7 +28247,7 @@
         <v>221</v>
       </c>
       <c r="J12" t="n">
-        <v>221</v>
+        <v>18.66944844484024</v>
       </c>
       <c r="K12" t="n">
         <v>221</v>
@@ -28256,7 +28256,7 @@
         <v>221</v>
       </c>
       <c r="M12" t="n">
-        <v>18.66944844484034</v>
+        <v>221</v>
       </c>
       <c r="N12" t="n">
         <v>221</v>
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I14" t="n">
         <v>146.0515516424836</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="V14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Y14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I15" t="n">
-        <v>234.9691117445034</v>
+        <v>244</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="L15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="N15" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>243</v>
+        <v>214.6645509853969</v>
       </c>
       <c r="R15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="V15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Y15" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="V16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Y16" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17">
@@ -28730,7 +28730,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>254.482120621149</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -28739,7 +28739,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>254.4821206211491</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>284</v>
@@ -29213,7 +29213,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>254.4821206211491</v>
+        <v>254.4821206211489</v>
       </c>
       <c r="Q24" t="n">
         <v>284</v>
@@ -29675,13 +29675,13 @@
         <v>221</v>
       </c>
       <c r="L30" t="n">
-        <v>18.6694484448401</v>
+        <v>221</v>
       </c>
       <c r="M30" t="n">
         <v>221</v>
       </c>
       <c r="N30" t="n">
-        <v>221</v>
+        <v>18.66944844484013</v>
       </c>
       <c r="O30" t="n">
         <v>221</v>
@@ -29903,28 +29903,28 @@
         <v>270</v>
       </c>
       <c r="I33" t="n">
+        <v>215.2009141932353</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>270</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11.54505705540018</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>270</v>
-      </c>
-      <c r="K33" t="n">
-        <v>226.7459712486357</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>270</v>
@@ -29976,7 +29976,7 @@
         <v>270</v>
       </c>
       <c r="G34" t="n">
-        <v>270</v>
+        <v>262.6904035872182</v>
       </c>
       <c r="H34" t="n">
         <v>270</v>
@@ -30143,7 +30143,7 @@
         <v>270</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>226.7459712486358</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30155,7 +30155,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>226.745971248636</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -30213,7 +30213,7 @@
         <v>270</v>
       </c>
       <c r="G37" t="n">
-        <v>270</v>
+        <v>262.6904035872328</v>
       </c>
       <c r="H37" t="n">
         <v>270</v>
@@ -30377,28 +30377,28 @@
         <v>270</v>
       </c>
       <c r="I39" t="n">
+        <v>215.2009141932353</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11.54505705540043</v>
+      </c>
+      <c r="K39" t="n">
         <v>270</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>270</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
-        <v>226.7459712486358</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>270</v>
@@ -30450,7 +30450,7 @@
         <v>270</v>
       </c>
       <c r="G40" t="n">
-        <v>270</v>
+        <v>262.6904035872346</v>
       </c>
       <c r="H40" t="n">
         <v>270</v>
@@ -30620,7 +30620,7 @@
         <v>220</v>
       </c>
       <c r="K42" t="n">
-        <v>220</v>
+        <v>31.76989627417115</v>
       </c>
       <c r="L42" t="n">
         <v>220</v>
@@ -30629,7 +30629,7 @@
         <v>220</v>
       </c>
       <c r="N42" t="n">
-        <v>89.78894412401721</v>
+        <v>220</v>
       </c>
       <c r="O42" t="n">
         <v>220</v>
@@ -30638,7 +30638,7 @@
         <v>220</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.9405481093475</v>
+        <v>220</v>
       </c>
       <c r="R42" t="n">
         <v>220</v>
@@ -30693,7 +30693,7 @@
         <v>220</v>
       </c>
       <c r="I43" t="n">
-        <v>204.1402507734851</v>
+        <v>211.1355369680604</v>
       </c>
       <c r="J43" t="n">
         <v>220</v>
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I44" t="n">
         <v>146.0515516424836</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45">
@@ -30830,76 +30830,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K45" t="n">
-        <v>198</v>
+        <v>83.36968751364684</v>
       </c>
       <c r="L45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P45" t="n">
-        <v>57.81967519632232</v>
+        <v>197</v>
       </c>
       <c r="Q45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y45" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I46" t="n">
         <v>175.2234884070035</v>
       </c>
       <c r="J46" t="n">
-        <v>159.7682719011811</v>
+        <v>109.2132501405745</v>
       </c>
       <c r="K46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U46" t="n">
         <v>150.9558338974088</v>
       </c>
       <c r="V46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y46" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -34746,10 +34746,10 @@
         <v>795</v>
       </c>
       <c r="K2" t="n">
-        <v>745.3952328643563</v>
+        <v>795</v>
       </c>
       <c r="L2" t="n">
-        <v>795</v>
+        <v>745.3952328643338</v>
       </c>
       <c r="M2" t="n">
         <v>795</v>
@@ -34880,31 +34880,31 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.0030124043716</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.6457263573978</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>224.7765115929965</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>368.0458380493382</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>88.29820671041094</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>38.44360226435771</v>
       </c>
       <c r="T4" t="n">
-        <v>110.4660025842623</v>
+        <v>190.1757613625948</v>
       </c>
       <c r="U4" t="n">
         <v>249.0441661025912</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,10 +34983,10 @@
         <v>795</v>
       </c>
       <c r="K5" t="n">
-        <v>745.3952328644162</v>
+        <v>745.3952328644218</v>
       </c>
       <c r="L5" t="n">
-        <v>795</v>
+        <v>795.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>795</v>
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94.79878946713337</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.0030124043716</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.6457263573978</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>224.7765115929965</v>
+        <v>16.50681274773828</v>
       </c>
       <c r="J7" t="n">
         <v>368.0458380493382</v>
       </c>
       <c r="K7" t="n">
-        <v>116.9264393136111</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>38.44360226435771</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>190.1757613625948</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,7 +35223,7 @@
         <v>795</v>
       </c>
       <c r="L8" t="n">
-        <v>745.3952328643859</v>
+        <v>745.3952328643513</v>
       </c>
       <c r="M8" t="n">
         <v>795</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>57.36208375076859</v>
+        <v>70.07268900487547</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.0030124043716</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>224.7765115929965</v>
       </c>
       <c r="J10" t="n">
-        <v>368.0458380493382</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>116.9264393136111</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>38.44360226435771</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.1757613625948</v>
       </c>
       <c r="U10" t="n">
         <v>249.0441661025912</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>404.1329564717196</v>
       </c>
       <c r="K11" t="n">
-        <v>730.170785864808</v>
+        <v>730.1707858648081</v>
       </c>
       <c r="L11" t="n">
-        <v>16.49445226130649</v>
+        <v>795</v>
       </c>
       <c r="M11" t="n">
         <v>534.3621741894223</v>
       </c>
       <c r="N11" t="n">
-        <v>638.0646955747317</v>
+        <v>215.1527937077123</v>
       </c>
       <c r="O11" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>14.74342237137889</v>
       </c>
       <c r="Q11" t="n">
-        <v>419.0432576171409</v>
+        <v>454.3166552737466</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>5.799085806764674</v>
       </c>
       <c r="J12" t="n">
-        <v>351.4922477471097</v>
+        <v>149.1616961919499</v>
       </c>
       <c r="K12" t="n">
         <v>421.1344395464517</v>
@@ -35542,7 +35542,7 @@
         <v>507.2341111977436</v>
       </c>
       <c r="M12" t="n">
-        <v>119.7894906093446</v>
+        <v>322.1200421645043</v>
       </c>
       <c r="N12" t="n">
         <v>370.1715878445039</v>
@@ -35694,10 +35694,10 @@
         <v>404.1329564717196</v>
       </c>
       <c r="K14" t="n">
-        <v>13.29566834170856</v>
+        <v>730.1707858648081</v>
       </c>
       <c r="L14" t="n">
-        <v>748.2798709298271</v>
+        <v>16.49445226130661</v>
       </c>
       <c r="M14" t="n">
         <v>534.3621741894223</v>
@@ -35712,7 +35712,7 @@
         <v>14.74342237137889</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>14.91030114542065</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>19.76819755126809</v>
+        <v>28.79908580676467</v>
       </c>
       <c r="J15" t="n">
-        <v>130.4922477471097</v>
+        <v>374.4922477471097</v>
       </c>
       <c r="K15" t="n">
-        <v>200.1344395464517</v>
+        <v>444.1344395464517</v>
       </c>
       <c r="L15" t="n">
-        <v>529.2341111977436</v>
+        <v>530.2341111977436</v>
       </c>
       <c r="M15" t="n">
-        <v>101.1200421645043</v>
+        <v>345.1200421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>392.1715878445039</v>
+        <v>149.1715878445039</v>
       </c>
       <c r="O15" t="n">
-        <v>497.7628898272747</v>
+        <v>254.7628898272747</v>
       </c>
       <c r="P15" t="n">
-        <v>367.3451365901249</v>
+        <v>124.3451365901249</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.0594518906525</v>
+        <v>48.7240028760494</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14.64572635739777</v>
+        <v>15.64572635739777</v>
       </c>
       <c r="I16" t="n">
-        <v>67.77651159299648</v>
+        <v>68.77651159299648</v>
       </c>
       <c r="J16" t="n">
-        <v>211.0458380493381</v>
+        <v>212.0458380493381</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,16 +35879,16 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>33.17576136259475</v>
+        <v>34.17576136259475</v>
       </c>
       <c r="U16" t="n">
-        <v>92.04416610259125</v>
+        <v>93.04416610259125</v>
       </c>
       <c r="V16" t="n">
-        <v>43.82968978378381</v>
+        <v>44.82968978378381</v>
       </c>
       <c r="W16" t="n">
-        <v>16.62719016129032</v>
+        <v>17.62719016129032</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>404.1329564717196</v>
       </c>
       <c r="K17" t="n">
-        <v>13.29566834170856</v>
+        <v>730.1707858648081</v>
       </c>
       <c r="L17" t="n">
-        <v>795.0000000000001</v>
+        <v>795</v>
       </c>
       <c r="M17" t="n">
         <v>534.3621741894223</v>
@@ -35943,13 +35943,13 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O17" t="n">
-        <v>293.9632156560805</v>
+        <v>31.40475340672705</v>
       </c>
       <c r="P17" t="n">
         <v>14.74342237137889</v>
       </c>
       <c r="Q17" t="n">
-        <v>454.3166552737466</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
         <v>286.2341111977436</v>
       </c>
       <c r="M18" t="n">
-        <v>101.1200421645043</v>
+        <v>355.6021627856532</v>
       </c>
       <c r="N18" t="n">
         <v>149.1715878445039</v>
@@ -36025,7 +36025,7 @@
         <v>254.7628898272747</v>
       </c>
       <c r="P18" t="n">
-        <v>378.8272572112741</v>
+        <v>124.3451365901249</v>
       </c>
       <c r="Q18" t="n">
         <v>118.0594518906525</v>
@@ -36168,10 +36168,10 @@
         <v>404.1329564717196</v>
       </c>
       <c r="K20" t="n">
-        <v>730.1707858648081</v>
+        <v>305.5078541078616</v>
       </c>
       <c r="L20" t="n">
-        <v>16.49445226130661</v>
+        <v>16.49445226130649</v>
       </c>
       <c r="M20" t="n">
         <v>534.3621741894223</v>
@@ -36180,10 +36180,10 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O20" t="n">
-        <v>355.5936458716744</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>14.74342237137889</v>
+        <v>795</v>
       </c>
       <c r="Q20" t="n">
         <v>454.3166552737466</v>
@@ -36405,10 +36405,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>711.3918404695087</v>
+        <v>730.170785864808</v>
       </c>
       <c r="L23" t="n">
-        <v>795</v>
+        <v>16.49445226130649</v>
       </c>
       <c r="M23" t="n">
         <v>534.3621741894223</v>
@@ -36417,7 +36417,7 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>759.7266023433941</v>
       </c>
       <c r="P23" t="n">
         <v>14.74342237137889</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>68.79908580676468</v>
+        <v>68.79908580676467</v>
       </c>
       <c r="J24" t="n">
         <v>130.4922477471097</v>
@@ -36499,7 +36499,7 @@
         <v>254.7628898272747</v>
       </c>
       <c r="P24" t="n">
-        <v>378.8272572112741</v>
+        <v>378.8272572112738</v>
       </c>
       <c r="Q24" t="n">
         <v>118.0594518906525</v>
@@ -36551,10 +36551,10 @@
         <v>9.617144032258068</v>
       </c>
       <c r="G25" t="n">
-        <v>39.00301240437161</v>
+        <v>39.00301240437162</v>
       </c>
       <c r="H25" t="n">
-        <v>55.64572635739778</v>
+        <v>55.64572635739776</v>
       </c>
       <c r="I25" t="n">
         <v>108.7765115929965</v>
@@ -36563,7 +36563,7 @@
         <v>252.0458380493381</v>
       </c>
       <c r="K25" t="n">
-        <v>0.92643931361106</v>
+        <v>0.9264393136110698</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>74.17576136259474</v>
+        <v>74.17576136259476</v>
       </c>
       <c r="U25" t="n">
         <v>133.0441661025912</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>317.5714168361906</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>13.29566834170856</v>
+        <v>13.29566834170855</v>
       </c>
       <c r="L26" t="n">
-        <v>16.49445226130655</v>
+        <v>671</v>
       </c>
       <c r="M26" t="n">
         <v>534.3621741894223</v>
@@ -36654,7 +36654,7 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O26" t="n">
-        <v>672</v>
+        <v>331.1062731379011</v>
       </c>
       <c r="P26" t="n">
         <v>14.74342237137889</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5.799085806764674</v>
+        <v>5.799085806764666</v>
       </c>
       <c r="J27" t="n">
         <v>351.4922477471097</v>
@@ -36739,7 +36739,7 @@
         <v>345.3451365901249</v>
       </c>
       <c r="Q27" t="n">
-        <v>55.05945189065249</v>
+        <v>55.05945189065248</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>11.17576136259474</v>
+        <v>11.17576136259476</v>
       </c>
       <c r="U28" t="n">
         <v>70.04416610259125</v>
@@ -36879,10 +36879,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>13.29566834170854</v>
+        <v>671</v>
       </c>
       <c r="L29" t="n">
-        <v>334.0658690974971</v>
+        <v>16.49445226130649</v>
       </c>
       <c r="M29" t="n">
         <v>534.3621741894223</v>
@@ -36891,7 +36891,7 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O29" t="n">
-        <v>672</v>
+        <v>327.9074892183031</v>
       </c>
       <c r="P29" t="n">
         <v>14.74342237137889</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>5.799085806764666</v>
+        <v>5.799085806764674</v>
       </c>
       <c r="J30" t="n">
         <v>351.4922477471097</v>
@@ -36961,13 +36961,13 @@
         <v>421.1344395464517</v>
       </c>
       <c r="L30" t="n">
-        <v>304.9035596425837</v>
+        <v>507.2341111977436</v>
       </c>
       <c r="M30" t="n">
         <v>322.1200421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>370.1715878445039</v>
+        <v>167.841036289344</v>
       </c>
       <c r="O30" t="n">
         <v>475.7628898272747</v>
@@ -36976,7 +36976,7 @@
         <v>345.3451365901249</v>
       </c>
       <c r="Q30" t="n">
-        <v>55.05945189065248</v>
+        <v>55.05945189065249</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>11.17576136259476</v>
+        <v>11.17576136259474</v>
       </c>
       <c r="U31" t="n">
         <v>70.04416610259125</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>672.0000000000001</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="K32" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L32" t="n">
-        <v>542.8173673673937</v>
+        <v>671</v>
       </c>
       <c r="M32" t="n">
-        <v>672</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="N32" t="n">
-        <v>672.0000000000001</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="O32" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P32" t="n">
-        <v>672.0000000000001</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="Q32" t="n">
-        <v>672.0000000000001</v>
+        <v>671.0000000000274</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,13 +37189,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>54.79908580676467</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>400.4922477471097</v>
+        <v>130.4922477471097</v>
       </c>
       <c r="K33" t="n">
-        <v>426.8804107950874</v>
+        <v>470.1344395464517</v>
       </c>
       <c r="L33" t="n">
         <v>286.2341111977436</v>
@@ -37204,13 +37204,13 @@
         <v>101.1200421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>149.1715878445039</v>
+        <v>160.7166448999041</v>
       </c>
       <c r="O33" t="n">
         <v>254.7628898272747</v>
       </c>
       <c r="P33" t="n">
-        <v>124.3451365901249</v>
+        <v>394.3451365901249</v>
       </c>
       <c r="Q33" t="n">
         <v>104.0594518906525</v>
@@ -37262,7 +37262,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>25.00301240437161</v>
+        <v>17.69341599158983</v>
       </c>
       <c r="H34" t="n">
         <v>41.64572635739778</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>672</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="K35" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L35" t="n">
-        <v>542.8173673673797</v>
+        <v>671</v>
       </c>
       <c r="M35" t="n">
-        <v>672</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="N35" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O35" t="n">
-        <v>672</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="P35" t="n">
-        <v>672</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="Q35" t="n">
-        <v>672</v>
+        <v>671.0000000000401</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>54.79908580676467</v>
       </c>
       <c r="J36" t="n">
-        <v>130.4922477471097</v>
+        <v>357.2382189957455</v>
       </c>
       <c r="K36" t="n">
         <v>200.1344395464517</v>
@@ -37441,7 +37441,7 @@
         <v>101.1200421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>375.9175590931399</v>
+        <v>149.1715878445039</v>
       </c>
       <c r="O36" t="n">
         <v>254.7628898272747</v>
@@ -37499,10 +37499,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>25.00301240437161</v>
+        <v>17.69341599160438</v>
       </c>
       <c r="H37" t="n">
-        <v>41.64572635739778</v>
+        <v>41.64572635739776</v>
       </c>
       <c r="I37" t="n">
         <v>94.77651159299648</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>60.17576136259475</v>
+        <v>60.17576136259476</v>
       </c>
       <c r="U37" t="n">
         <v>119.0441661025912</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="K38" t="n">
-        <v>672</v>
+        <v>670.9999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>542.8173673673153</v>
+        <v>671</v>
       </c>
       <c r="M38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="N38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="O38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="P38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="Q38" t="n">
-        <v>672</v>
+        <v>671.0000000000374</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,16 +37663,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>54.79908580676467</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>130.4922477471097</v>
+        <v>142.0373048025101</v>
       </c>
       <c r="K39" t="n">
-        <v>200.1344395464517</v>
+        <v>470.1344395464517</v>
       </c>
       <c r="L39" t="n">
-        <v>556.2341111977436</v>
+        <v>286.2341111977436</v>
       </c>
       <c r="M39" t="n">
         <v>101.1200421645043</v>
@@ -37681,10 +37681,10 @@
         <v>149.1715878445039</v>
       </c>
       <c r="O39" t="n">
-        <v>254.7628898272747</v>
+        <v>524.7628898272746</v>
       </c>
       <c r="P39" t="n">
-        <v>351.0911078387608</v>
+        <v>124.3451365901249</v>
       </c>
       <c r="Q39" t="n">
         <v>104.0594518906525</v>
@@ -37736,10 +37736,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>25.00301240437161</v>
+        <v>17.6934159916062</v>
       </c>
       <c r="H40" t="n">
-        <v>41.64572635739778</v>
+        <v>41.64572635739776</v>
       </c>
       <c r="I40" t="n">
         <v>94.77651159299648</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>60.17576136259475</v>
+        <v>60.17576136259476</v>
       </c>
       <c r="U40" t="n">
         <v>119.0441661025912</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>334.0658690974971</v>
+        <v>404.1329564717196</v>
       </c>
       <c r="K41" t="n">
         <v>13.29566834170856</v>
       </c>
       <c r="L41" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="M41" t="n">
         <v>534.3621741894223</v>
       </c>
       <c r="N41" t="n">
-        <v>638.0646955747317</v>
+        <v>565.0380122409131</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -37906,7 +37906,7 @@
         <v>350.4922477471097</v>
       </c>
       <c r="K42" t="n">
-        <v>420.1344395464517</v>
+        <v>231.9043358206228</v>
       </c>
       <c r="L42" t="n">
         <v>506.2341111977436</v>
@@ -37915,7 +37915,7 @@
         <v>321.1200421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>238.9605319685211</v>
+        <v>369.1715878445039</v>
       </c>
       <c r="O42" t="n">
         <v>474.7628898272747</v>
@@ -37924,7 +37924,7 @@
         <v>344.3451365901249</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>54.05945189065249</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,7 +37979,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>28.91676236648155</v>
+        <v>35.91204856105691</v>
       </c>
       <c r="J43" t="n">
         <v>188.0458380493381</v>
@@ -38064,10 +38064,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>345.610507549278</v>
+        <v>671</v>
       </c>
       <c r="L44" t="n">
-        <v>16.49445226130655</v>
+        <v>16.49445226130649</v>
       </c>
       <c r="M44" t="n">
         <v>534.3621741894223</v>
@@ -38076,13 +38076,13 @@
         <v>638.0646955747317</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>671.0000000000747</v>
       </c>
       <c r="P44" t="n">
-        <v>672</v>
+        <v>125.9675668633536</v>
       </c>
       <c r="Q44" t="n">
-        <v>454.3166552737466</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,28 +38140,28 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>328.4922477471097</v>
+        <v>327.4922477471097</v>
       </c>
       <c r="K45" t="n">
-        <v>398.1344395464517</v>
+        <v>283.5041270600985</v>
       </c>
       <c r="L45" t="n">
-        <v>484.2341111977436</v>
+        <v>483.2341111977436</v>
       </c>
       <c r="M45" t="n">
-        <v>299.1200421645043</v>
+        <v>298.1200421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>347.1715878445039</v>
+        <v>346.1715878445039</v>
       </c>
       <c r="O45" t="n">
-        <v>452.7628898272747</v>
+        <v>451.7628898272747</v>
       </c>
       <c r="P45" t="n">
-        <v>182.1648117864472</v>
+        <v>321.3451365901249</v>
       </c>
       <c r="Q45" t="n">
-        <v>32.05945189065249</v>
+        <v>31.05945189065249</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>127.8141099505192</v>
+        <v>77.25908818991262</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
